--- a/output/第10期計画_見える化_入力箇所と入力値.xlsx
+++ b/output/第10期計画_見える化_入力箇所と入力値.xlsx
@@ -1095,13 +1095,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -1112,6 +1112,7 @@
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1124,16 +1125,17 @@
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>【暫定値】　本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。　「地域支援事業」の画面に入れる値です。この画面は量（利用者数）と事業費（円）が同じ表に並ぶ様式です。事業費は年間累計の円、利用者数は1月当たりの人数です。量の欄があるのは4項目だけで、ほかの事業は事業費の欄しかありません。行の並びは国の様式（ワークシート）によります。</t>
+          <t>【暫定値】　本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。　「地域支援事業」の画面に入れる値です。この画面は量（利用者数）と事業費（円）が同じ表に並ぶ様式です。事業費は年間累計の円、利用者数は1月当たりの人数です。量の欄があるのは4項目だけで、ほかの事業は事業費の欄しかありません。行の並びは国の様式（ワークシート）によります。量（手順6）と事業費（手順7）が別の画面になっている場合は、「手順」の欄で行を絞ってお使いください。</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="72" customHeight="1">
       <c r="A4" s="31" t="inlineStr">
         <is>
           <t>【この画面の値は特に暫定の度合いが高いものです】
-事業別の内訳（総合事業22項目・包括的支援事業8項目）は未受領です（確認事項No.5・No.112・No.150）。入れられるのは総合事業費の計と包括的支援事業・任意事業費の計、及び量3項目です。未受領の欄は空欄のままとし、0を入れません（0を入れると「計上がない」ことを表してしまいます）。</t>
+事業別の内訳（総合事業22項目・包括的支援事業8項目）は未受領です（確認事項No.5・No.112・No.150）。入れられるのは総合事業費の計と包括的支援事業・任意事業費の計、及び量3項目です。未受領の欄は空欄のままとし、0を入れません（0を入れると「計上がない」ことを表してしまいます）。
+量（手順6）と事業費（手順7）は、システムでは別の画面に分かれていることがあります。その場合は「手順」の欄で行を絞り、手順6には量（人／月）の行、手順7には事業費（円）の行をお入れください。行の並びと項目名はどちらの画面でも同じです。</t>
         </is>
       </c>
     </row>
@@ -1154,60 +1156,65 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>令和6年度</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>令和7年度</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>令和8年度</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>令和12年度</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>令和17年度</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>令和27年度</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>令和32年度</t>
         </is>
@@ -1222,20 +1229,25 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr"/>
       <c r="E8" s="13" t="inlineStr"/>
       <c r="F8" s="13" t="inlineStr"/>
-      <c r="G8" s="32" t="inlineStr"/>
+      <c r="G8" s="13" t="inlineStr"/>
       <c r="H8" s="32" t="inlineStr"/>
       <c r="I8" s="32" t="inlineStr"/>
-      <c r="J8" s="13" t="inlineStr"/>
+      <c r="J8" s="32" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
       <c r="L8" s="13" t="inlineStr"/>
       <c r="M8" s="13" t="inlineStr"/>
       <c r="N8" s="13" t="inlineStr"/>
+      <c r="O8" s="13" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="5" t="inlineStr"/>
@@ -1246,28 +1258,33 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
+          <t>手順6</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
           <t>量（人／月）</t>
         </is>
       </c>
-      <c r="D9" s="33" t="n">
+      <c r="E9" s="33" t="n">
         <v>75</v>
       </c>
-      <c r="E9" s="33" t="inlineStr"/>
       <c r="F9" s="33" t="inlineStr"/>
-      <c r="G9" s="24" t="n">
+      <c r="G9" s="33" t="inlineStr"/>
+      <c r="H9" s="24" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="H9" s="24" t="n">
+      <c r="I9" s="24" t="n">
         <v>77.3</v>
       </c>
-      <c r="I9" s="24" t="n">
+      <c r="J9" s="24" t="n">
         <v>78.2</v>
       </c>
-      <c r="J9" s="33" t="inlineStr"/>
       <c r="K9" s="33" t="inlineStr"/>
       <c r="L9" s="33" t="inlineStr"/>
       <c r="M9" s="33" t="inlineStr"/>
       <c r="N9" s="33" t="inlineStr"/>
+      <c r="O9" s="33" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="5" t="inlineStr"/>
@@ -1278,20 +1295,25 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr"/>
       <c r="E10" s="13" t="inlineStr"/>
       <c r="F10" s="13" t="inlineStr"/>
-      <c r="G10" s="32" t="inlineStr"/>
+      <c r="G10" s="13" t="inlineStr"/>
       <c r="H10" s="32" t="inlineStr"/>
       <c r="I10" s="32" t="inlineStr"/>
-      <c r="J10" s="13" t="inlineStr"/>
+      <c r="J10" s="32" t="inlineStr"/>
       <c r="K10" s="13" t="inlineStr"/>
       <c r="L10" s="13" t="inlineStr"/>
       <c r="M10" s="13" t="inlineStr"/>
       <c r="N10" s="13" t="inlineStr"/>
+      <c r="O10" s="13" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="5" t="inlineStr"/>
@@ -1302,20 +1324,25 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
+          <t>手順6</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
           <t>量（人／月）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr"/>
       <c r="E11" s="25" t="inlineStr"/>
       <c r="F11" s="25" t="inlineStr"/>
-      <c r="G11" s="34" t="inlineStr"/>
+      <c r="G11" s="25" t="inlineStr"/>
       <c r="H11" s="34" t="inlineStr"/>
       <c r="I11" s="34" t="inlineStr"/>
-      <c r="J11" s="25" t="inlineStr"/>
+      <c r="J11" s="34" t="inlineStr"/>
       <c r="K11" s="25" t="inlineStr"/>
       <c r="L11" s="25" t="inlineStr"/>
       <c r="M11" s="25" t="inlineStr"/>
       <c r="N11" s="25" t="inlineStr"/>
+      <c r="O11" s="25" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="5" t="inlineStr"/>
@@ -1326,20 +1353,25 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr"/>
       <c r="E12" s="13" t="inlineStr"/>
       <c r="F12" s="13" t="inlineStr"/>
-      <c r="G12" s="32" t="inlineStr"/>
+      <c r="G12" s="13" t="inlineStr"/>
       <c r="H12" s="32" t="inlineStr"/>
       <c r="I12" s="32" t="inlineStr"/>
-      <c r="J12" s="13" t="inlineStr"/>
+      <c r="J12" s="32" t="inlineStr"/>
       <c r="K12" s="13" t="inlineStr"/>
       <c r="L12" s="13" t="inlineStr"/>
       <c r="M12" s="13" t="inlineStr"/>
       <c r="N12" s="13" t="inlineStr"/>
+      <c r="O12" s="13" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="5" t="inlineStr"/>
@@ -1350,20 +1382,25 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr"/>
       <c r="E13" s="13" t="inlineStr"/>
       <c r="F13" s="13" t="inlineStr"/>
-      <c r="G13" s="32" t="inlineStr"/>
+      <c r="G13" s="13" t="inlineStr"/>
       <c r="H13" s="32" t="inlineStr"/>
       <c r="I13" s="32" t="inlineStr"/>
-      <c r="J13" s="13" t="inlineStr"/>
+      <c r="J13" s="32" t="inlineStr"/>
       <c r="K13" s="13" t="inlineStr"/>
       <c r="L13" s="13" t="inlineStr"/>
       <c r="M13" s="13" t="inlineStr"/>
       <c r="N13" s="13" t="inlineStr"/>
+      <c r="O13" s="13" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="5" t="inlineStr"/>
@@ -1374,20 +1411,25 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr"/>
       <c r="E14" s="13" t="inlineStr"/>
       <c r="F14" s="13" t="inlineStr"/>
-      <c r="G14" s="32" t="inlineStr"/>
+      <c r="G14" s="13" t="inlineStr"/>
       <c r="H14" s="32" t="inlineStr"/>
       <c r="I14" s="32" t="inlineStr"/>
-      <c r="J14" s="13" t="inlineStr"/>
+      <c r="J14" s="32" t="inlineStr"/>
       <c r="K14" s="13" t="inlineStr"/>
       <c r="L14" s="13" t="inlineStr"/>
       <c r="M14" s="13" t="inlineStr"/>
       <c r="N14" s="13" t="inlineStr"/>
+      <c r="O14" s="13" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="5" t="inlineStr"/>
@@ -1398,20 +1440,25 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr"/>
       <c r="E15" s="13" t="inlineStr"/>
       <c r="F15" s="13" t="inlineStr"/>
-      <c r="G15" s="32" t="inlineStr"/>
+      <c r="G15" s="13" t="inlineStr"/>
       <c r="H15" s="32" t="inlineStr"/>
       <c r="I15" s="32" t="inlineStr"/>
-      <c r="J15" s="13" t="inlineStr"/>
+      <c r="J15" s="32" t="inlineStr"/>
       <c r="K15" s="13" t="inlineStr"/>
       <c r="L15" s="13" t="inlineStr"/>
       <c r="M15" s="13" t="inlineStr"/>
       <c r="N15" s="13" t="inlineStr"/>
+      <c r="O15" s="13" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="5" t="inlineStr"/>
@@ -1422,20 +1469,25 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr"/>
       <c r="E16" s="13" t="inlineStr"/>
       <c r="F16" s="13" t="inlineStr"/>
-      <c r="G16" s="32" t="inlineStr"/>
+      <c r="G16" s="13" t="inlineStr"/>
       <c r="H16" s="32" t="inlineStr"/>
       <c r="I16" s="32" t="inlineStr"/>
-      <c r="J16" s="13" t="inlineStr"/>
+      <c r="J16" s="32" t="inlineStr"/>
       <c r="K16" s="13" t="inlineStr"/>
       <c r="L16" s="13" t="inlineStr"/>
       <c r="M16" s="13" t="inlineStr"/>
       <c r="N16" s="13" t="inlineStr"/>
+      <c r="O16" s="13" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="5" t="inlineStr"/>
@@ -1446,28 +1498,33 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
+          <t>手順6</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
           <t>量（人／月）</t>
         </is>
       </c>
-      <c r="D17" s="33" t="n">
+      <c r="E17" s="33" t="n">
         <v>40</v>
       </c>
-      <c r="E17" s="33" t="inlineStr"/>
       <c r="F17" s="33" t="inlineStr"/>
-      <c r="G17" s="24" t="n">
+      <c r="G17" s="33" t="inlineStr"/>
+      <c r="H17" s="24" t="n">
         <v>40.8</v>
       </c>
-      <c r="H17" s="24" t="n">
+      <c r="I17" s="24" t="n">
         <v>41.3</v>
       </c>
-      <c r="I17" s="24" t="n">
+      <c r="J17" s="24" t="n">
         <v>41.7</v>
       </c>
-      <c r="J17" s="33" t="inlineStr"/>
       <c r="K17" s="33" t="inlineStr"/>
       <c r="L17" s="33" t="inlineStr"/>
       <c r="M17" s="33" t="inlineStr"/>
       <c r="N17" s="33" t="inlineStr"/>
+      <c r="O17" s="33" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="5" t="inlineStr"/>
@@ -1478,20 +1535,25 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr"/>
       <c r="E18" s="13" t="inlineStr"/>
       <c r="F18" s="13" t="inlineStr"/>
-      <c r="G18" s="32" t="inlineStr"/>
+      <c r="G18" s="13" t="inlineStr"/>
       <c r="H18" s="32" t="inlineStr"/>
       <c r="I18" s="32" t="inlineStr"/>
-      <c r="J18" s="13" t="inlineStr"/>
+      <c r="J18" s="32" t="inlineStr"/>
       <c r="K18" s="13" t="inlineStr"/>
       <c r="L18" s="13" t="inlineStr"/>
       <c r="M18" s="13" t="inlineStr"/>
       <c r="N18" s="13" t="inlineStr"/>
+      <c r="O18" s="13" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="5" t="inlineStr"/>
@@ -1502,28 +1564,33 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
+          <t>手順6</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
           <t>量（人／月）</t>
         </is>
       </c>
-      <c r="D19" s="33" t="n">
+      <c r="E19" s="33" t="n">
         <v>149</v>
       </c>
-      <c r="E19" s="33" t="inlineStr"/>
       <c r="F19" s="33" t="inlineStr"/>
-      <c r="G19" s="24" t="n">
+      <c r="G19" s="33" t="inlineStr"/>
+      <c r="H19" s="24" t="n">
         <v>152.1</v>
       </c>
-      <c r="H19" s="24" t="n">
+      <c r="I19" s="24" t="n">
         <v>153.7</v>
       </c>
-      <c r="I19" s="24" t="n">
+      <c r="J19" s="24" t="n">
         <v>155.3</v>
       </c>
-      <c r="J19" s="33" t="inlineStr"/>
       <c r="K19" s="33" t="inlineStr"/>
       <c r="L19" s="33" t="inlineStr"/>
       <c r="M19" s="33" t="inlineStr"/>
       <c r="N19" s="33" t="inlineStr"/>
+      <c r="O19" s="33" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="5" t="inlineStr"/>
@@ -1534,20 +1601,25 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr"/>
       <c r="E20" s="13" t="inlineStr"/>
       <c r="F20" s="13" t="inlineStr"/>
-      <c r="G20" s="32" t="inlineStr"/>
+      <c r="G20" s="13" t="inlineStr"/>
       <c r="H20" s="32" t="inlineStr"/>
       <c r="I20" s="32" t="inlineStr"/>
-      <c r="J20" s="13" t="inlineStr"/>
+      <c r="J20" s="32" t="inlineStr"/>
       <c r="K20" s="13" t="inlineStr"/>
       <c r="L20" s="13" t="inlineStr"/>
       <c r="M20" s="13" t="inlineStr"/>
       <c r="N20" s="13" t="inlineStr"/>
+      <c r="O20" s="13" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="5" t="inlineStr"/>
@@ -1558,20 +1630,25 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr"/>
       <c r="E21" s="13" t="inlineStr"/>
       <c r="F21" s="13" t="inlineStr"/>
-      <c r="G21" s="32" t="inlineStr"/>
+      <c r="G21" s="13" t="inlineStr"/>
       <c r="H21" s="32" t="inlineStr"/>
       <c r="I21" s="32" t="inlineStr"/>
-      <c r="J21" s="13" t="inlineStr"/>
+      <c r="J21" s="32" t="inlineStr"/>
       <c r="K21" s="13" t="inlineStr"/>
       <c r="L21" s="13" t="inlineStr"/>
       <c r="M21" s="13" t="inlineStr"/>
       <c r="N21" s="13" t="inlineStr"/>
+      <c r="O21" s="13" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="5" t="inlineStr"/>
@@ -1582,20 +1659,25 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr"/>
       <c r="E22" s="13" t="inlineStr"/>
       <c r="F22" s="13" t="inlineStr"/>
-      <c r="G22" s="32" t="inlineStr"/>
+      <c r="G22" s="13" t="inlineStr"/>
       <c r="H22" s="32" t="inlineStr"/>
       <c r="I22" s="32" t="inlineStr"/>
-      <c r="J22" s="13" t="inlineStr"/>
+      <c r="J22" s="32" t="inlineStr"/>
       <c r="K22" s="13" t="inlineStr"/>
       <c r="L22" s="13" t="inlineStr"/>
       <c r="M22" s="13" t="inlineStr"/>
       <c r="N22" s="13" t="inlineStr"/>
+      <c r="O22" s="13" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="5" t="inlineStr"/>
@@ -1606,20 +1688,25 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr"/>
       <c r="E23" s="13" t="inlineStr"/>
       <c r="F23" s="13" t="inlineStr"/>
-      <c r="G23" s="32" t="inlineStr"/>
+      <c r="G23" s="13" t="inlineStr"/>
       <c r="H23" s="32" t="inlineStr"/>
       <c r="I23" s="32" t="inlineStr"/>
-      <c r="J23" s="13" t="inlineStr"/>
+      <c r="J23" s="32" t="inlineStr"/>
       <c r="K23" s="13" t="inlineStr"/>
       <c r="L23" s="13" t="inlineStr"/>
       <c r="M23" s="13" t="inlineStr"/>
       <c r="N23" s="13" t="inlineStr"/>
+      <c r="O23" s="13" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="5" t="inlineStr"/>
@@ -1630,20 +1717,25 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
       <c r="E24" s="13" t="inlineStr"/>
       <c r="F24" s="13" t="inlineStr"/>
-      <c r="G24" s="32" t="inlineStr"/>
+      <c r="G24" s="13" t="inlineStr"/>
       <c r="H24" s="32" t="inlineStr"/>
       <c r="I24" s="32" t="inlineStr"/>
-      <c r="J24" s="13" t="inlineStr"/>
+      <c r="J24" s="32" t="inlineStr"/>
       <c r="K24" s="13" t="inlineStr"/>
       <c r="L24" s="13" t="inlineStr"/>
       <c r="M24" s="13" t="inlineStr"/>
       <c r="N24" s="13" t="inlineStr"/>
+      <c r="O24" s="13" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="5" t="inlineStr"/>
@@ -1654,20 +1746,25 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr"/>
       <c r="E25" s="13" t="inlineStr"/>
       <c r="F25" s="13" t="inlineStr"/>
-      <c r="G25" s="32" t="inlineStr"/>
+      <c r="G25" s="13" t="inlineStr"/>
       <c r="H25" s="32" t="inlineStr"/>
       <c r="I25" s="32" t="inlineStr"/>
-      <c r="J25" s="13" t="inlineStr"/>
+      <c r="J25" s="32" t="inlineStr"/>
       <c r="K25" s="13" t="inlineStr"/>
       <c r="L25" s="13" t="inlineStr"/>
       <c r="M25" s="13" t="inlineStr"/>
       <c r="N25" s="13" t="inlineStr"/>
+      <c r="O25" s="13" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="5" t="inlineStr"/>
@@ -1678,20 +1775,25 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr"/>
       <c r="F26" s="13" t="inlineStr"/>
-      <c r="G26" s="32" t="inlineStr"/>
+      <c r="G26" s="13" t="inlineStr"/>
       <c r="H26" s="32" t="inlineStr"/>
       <c r="I26" s="32" t="inlineStr"/>
-      <c r="J26" s="13" t="inlineStr"/>
+      <c r="J26" s="32" t="inlineStr"/>
       <c r="K26" s="13" t="inlineStr"/>
       <c r="L26" s="13" t="inlineStr"/>
       <c r="M26" s="13" t="inlineStr"/>
       <c r="N26" s="13" t="inlineStr"/>
+      <c r="O26" s="13" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="5" t="inlineStr"/>
@@ -1702,20 +1804,25 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr"/>
       <c r="E27" s="13" t="inlineStr"/>
       <c r="F27" s="13" t="inlineStr"/>
-      <c r="G27" s="32" t="inlineStr"/>
+      <c r="G27" s="13" t="inlineStr"/>
       <c r="H27" s="32" t="inlineStr"/>
       <c r="I27" s="32" t="inlineStr"/>
-      <c r="J27" s="13" t="inlineStr"/>
+      <c r="J27" s="32" t="inlineStr"/>
       <c r="K27" s="13" t="inlineStr"/>
       <c r="L27" s="13" t="inlineStr"/>
       <c r="M27" s="13" t="inlineStr"/>
       <c r="N27" s="13" t="inlineStr"/>
+      <c r="O27" s="13" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="5" t="inlineStr"/>
@@ -1726,20 +1833,25 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr"/>
       <c r="E28" s="13" t="inlineStr"/>
       <c r="F28" s="13" t="inlineStr"/>
-      <c r="G28" s="32" t="inlineStr"/>
+      <c r="G28" s="13" t="inlineStr"/>
       <c r="H28" s="32" t="inlineStr"/>
       <c r="I28" s="32" t="inlineStr"/>
-      <c r="J28" s="13" t="inlineStr"/>
+      <c r="J28" s="32" t="inlineStr"/>
       <c r="K28" s="13" t="inlineStr"/>
       <c r="L28" s="13" t="inlineStr"/>
       <c r="M28" s="13" t="inlineStr"/>
       <c r="N28" s="13" t="inlineStr"/>
+      <c r="O28" s="13" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="5" t="inlineStr"/>
@@ -1750,20 +1862,25 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr"/>
       <c r="E29" s="13" t="inlineStr"/>
       <c r="F29" s="13" t="inlineStr"/>
-      <c r="G29" s="32" t="inlineStr"/>
+      <c r="G29" s="13" t="inlineStr"/>
       <c r="H29" s="32" t="inlineStr"/>
       <c r="I29" s="32" t="inlineStr"/>
-      <c r="J29" s="13" t="inlineStr"/>
+      <c r="J29" s="32" t="inlineStr"/>
       <c r="K29" s="13" t="inlineStr"/>
       <c r="L29" s="13" t="inlineStr"/>
       <c r="M29" s="13" t="inlineStr"/>
       <c r="N29" s="13" t="inlineStr"/>
+      <c r="O29" s="13" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="5" t="inlineStr"/>
@@ -1774,20 +1891,25 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr"/>
       <c r="E30" s="13" t="inlineStr"/>
       <c r="F30" s="13" t="inlineStr"/>
-      <c r="G30" s="32" t="inlineStr"/>
+      <c r="G30" s="13" t="inlineStr"/>
       <c r="H30" s="32" t="inlineStr"/>
       <c r="I30" s="32" t="inlineStr"/>
-      <c r="J30" s="13" t="inlineStr"/>
+      <c r="J30" s="32" t="inlineStr"/>
       <c r="K30" s="13" t="inlineStr"/>
       <c r="L30" s="13" t="inlineStr"/>
       <c r="M30" s="13" t="inlineStr"/>
       <c r="N30" s="13" t="inlineStr"/>
+      <c r="O30" s="13" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="5" t="inlineStr"/>
@@ -1798,20 +1920,25 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr"/>
       <c r="E31" s="13" t="inlineStr"/>
       <c r="F31" s="13" t="inlineStr"/>
-      <c r="G31" s="32" t="inlineStr"/>
+      <c r="G31" s="13" t="inlineStr"/>
       <c r="H31" s="32" t="inlineStr"/>
       <c r="I31" s="32" t="inlineStr"/>
-      <c r="J31" s="13" t="inlineStr"/>
+      <c r="J31" s="32" t="inlineStr"/>
       <c r="K31" s="13" t="inlineStr"/>
       <c r="L31" s="13" t="inlineStr"/>
       <c r="M31" s="13" t="inlineStr"/>
       <c r="N31" s="13" t="inlineStr"/>
+      <c r="O31" s="13" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="5" t="inlineStr"/>
@@ -1822,20 +1949,25 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr"/>
       <c r="E32" s="13" t="inlineStr"/>
       <c r="F32" s="13" t="inlineStr"/>
-      <c r="G32" s="32" t="inlineStr"/>
+      <c r="G32" s="13" t="inlineStr"/>
       <c r="H32" s="32" t="inlineStr"/>
       <c r="I32" s="32" t="inlineStr"/>
-      <c r="J32" s="13" t="inlineStr"/>
+      <c r="J32" s="32" t="inlineStr"/>
       <c r="K32" s="13" t="inlineStr"/>
       <c r="L32" s="13" t="inlineStr"/>
       <c r="M32" s="13" t="inlineStr"/>
       <c r="N32" s="13" t="inlineStr"/>
+      <c r="O32" s="13" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="5" t="inlineStr"/>
@@ -1846,20 +1978,25 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr"/>
       <c r="E33" s="13" t="inlineStr"/>
       <c r="F33" s="13" t="inlineStr"/>
-      <c r="G33" s="32" t="inlineStr"/>
+      <c r="G33" s="13" t="inlineStr"/>
       <c r="H33" s="32" t="inlineStr"/>
       <c r="I33" s="32" t="inlineStr"/>
-      <c r="J33" s="13" t="inlineStr"/>
+      <c r="J33" s="32" t="inlineStr"/>
       <c r="K33" s="13" t="inlineStr"/>
       <c r="L33" s="13" t="inlineStr"/>
       <c r="M33" s="13" t="inlineStr"/>
       <c r="N33" s="13" t="inlineStr"/>
+      <c r="O33" s="13" t="inlineStr"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
@@ -1877,60 +2014,65 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>令和6年度</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>令和7年度</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>令和8年度</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>令和12年度</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
         <is>
           <t>令和17年度</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr">
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>令和27年度</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>令和32年度</t>
         </is>
@@ -1945,20 +2087,25 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr"/>
       <c r="E36" s="13" t="inlineStr"/>
       <c r="F36" s="13" t="inlineStr"/>
-      <c r="G36" s="32" t="inlineStr"/>
+      <c r="G36" s="13" t="inlineStr"/>
       <c r="H36" s="32" t="inlineStr"/>
       <c r="I36" s="32" t="inlineStr"/>
-      <c r="J36" s="13" t="inlineStr"/>
+      <c r="J36" s="32" t="inlineStr"/>
       <c r="K36" s="13" t="inlineStr"/>
       <c r="L36" s="13" t="inlineStr"/>
       <c r="M36" s="13" t="inlineStr"/>
       <c r="N36" s="13" t="inlineStr"/>
+      <c r="O36" s="13" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="5" t="inlineStr"/>
@@ -1969,20 +2116,25 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr"/>
       <c r="E37" s="13" t="inlineStr"/>
       <c r="F37" s="13" t="inlineStr"/>
-      <c r="G37" s="32" t="inlineStr"/>
+      <c r="G37" s="13" t="inlineStr"/>
       <c r="H37" s="32" t="inlineStr"/>
       <c r="I37" s="32" t="inlineStr"/>
-      <c r="J37" s="13" t="inlineStr"/>
+      <c r="J37" s="32" t="inlineStr"/>
       <c r="K37" s="13" t="inlineStr"/>
       <c r="L37" s="13" t="inlineStr"/>
       <c r="M37" s="13" t="inlineStr"/>
       <c r="N37" s="13" t="inlineStr"/>
+      <c r="O37" s="13" t="inlineStr"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
@@ -2000,60 +2152,65 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>令和6年度</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>令和7年度</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>令和8年度</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>令和12年度</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
         <is>
           <t>令和17年度</t>
         </is>
       </c>
-      <c r="L39" s="4" t="inlineStr">
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="M39" s="4" t="inlineStr">
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>令和27年度</t>
         </is>
       </c>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>令和32年度</t>
         </is>
@@ -2068,20 +2225,25 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="13" t="inlineStr"/>
       <c r="F40" s="13" t="inlineStr"/>
-      <c r="G40" s="32" t="inlineStr"/>
+      <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="32" t="inlineStr"/>
       <c r="I40" s="32" t="inlineStr"/>
-      <c r="J40" s="13" t="inlineStr"/>
+      <c r="J40" s="32" t="inlineStr"/>
       <c r="K40" s="13" t="inlineStr"/>
       <c r="L40" s="13" t="inlineStr"/>
       <c r="M40" s="13" t="inlineStr"/>
       <c r="N40" s="13" t="inlineStr"/>
+      <c r="O40" s="13" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="5" t="inlineStr"/>
@@ -2092,20 +2254,25 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr"/>
       <c r="E41" s="13" t="inlineStr"/>
       <c r="F41" s="13" t="inlineStr"/>
-      <c r="G41" s="32" t="inlineStr"/>
+      <c r="G41" s="13" t="inlineStr"/>
       <c r="H41" s="32" t="inlineStr"/>
       <c r="I41" s="32" t="inlineStr"/>
-      <c r="J41" s="13" t="inlineStr"/>
+      <c r="J41" s="32" t="inlineStr"/>
       <c r="K41" s="13" t="inlineStr"/>
       <c r="L41" s="13" t="inlineStr"/>
       <c r="M41" s="13" t="inlineStr"/>
       <c r="N41" s="13" t="inlineStr"/>
+      <c r="O41" s="13" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="5" t="inlineStr"/>
@@ -2116,20 +2283,25 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr"/>
       <c r="E42" s="13" t="inlineStr"/>
       <c r="F42" s="13" t="inlineStr"/>
-      <c r="G42" s="32" t="inlineStr"/>
+      <c r="G42" s="13" t="inlineStr"/>
       <c r="H42" s="32" t="inlineStr"/>
       <c r="I42" s="32" t="inlineStr"/>
-      <c r="J42" s="13" t="inlineStr"/>
+      <c r="J42" s="32" t="inlineStr"/>
       <c r="K42" s="13" t="inlineStr"/>
       <c r="L42" s="13" t="inlineStr"/>
       <c r="M42" s="13" t="inlineStr"/>
       <c r="N42" s="13" t="inlineStr"/>
+      <c r="O42" s="13" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="5" t="inlineStr"/>
@@ -2140,20 +2312,25 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr"/>
       <c r="E43" s="13" t="inlineStr"/>
       <c r="F43" s="13" t="inlineStr"/>
-      <c r="G43" s="32" t="inlineStr"/>
+      <c r="G43" s="13" t="inlineStr"/>
       <c r="H43" s="32" t="inlineStr"/>
       <c r="I43" s="32" t="inlineStr"/>
-      <c r="J43" s="13" t="inlineStr"/>
+      <c r="J43" s="32" t="inlineStr"/>
       <c r="K43" s="13" t="inlineStr"/>
       <c r="L43" s="13" t="inlineStr"/>
       <c r="M43" s="13" t="inlineStr"/>
       <c r="N43" s="13" t="inlineStr"/>
+      <c r="O43" s="13" t="inlineStr"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="5" t="inlineStr"/>
@@ -2164,20 +2341,25 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr"/>
       <c r="E44" s="13" t="inlineStr"/>
       <c r="F44" s="13" t="inlineStr"/>
-      <c r="G44" s="32" t="inlineStr"/>
+      <c r="G44" s="13" t="inlineStr"/>
       <c r="H44" s="32" t="inlineStr"/>
       <c r="I44" s="32" t="inlineStr"/>
-      <c r="J44" s="13" t="inlineStr"/>
+      <c r="J44" s="32" t="inlineStr"/>
       <c r="K44" s="13" t="inlineStr"/>
       <c r="L44" s="13" t="inlineStr"/>
       <c r="M44" s="13" t="inlineStr"/>
       <c r="N44" s="13" t="inlineStr"/>
+      <c r="O44" s="13" t="inlineStr"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="5" t="inlineStr"/>
@@ -2188,20 +2370,25 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
+          <t>手順7</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
       </c>
-      <c r="D45" s="13" t="inlineStr"/>
       <c r="E45" s="13" t="inlineStr"/>
       <c r="F45" s="13" t="inlineStr"/>
-      <c r="G45" s="32" t="inlineStr"/>
+      <c r="G45" s="13" t="inlineStr"/>
       <c r="H45" s="32" t="inlineStr"/>
       <c r="I45" s="32" t="inlineStr"/>
-      <c r="J45" s="13" t="inlineStr"/>
+      <c r="J45" s="32" t="inlineStr"/>
       <c r="K45" s="13" t="inlineStr"/>
       <c r="L45" s="13" t="inlineStr"/>
       <c r="M45" s="13" t="inlineStr"/>
       <c r="N45" s="13" t="inlineStr"/>
+      <c r="O45" s="13" t="inlineStr"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
@@ -2219,60 +2406,65 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>令和6年度</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>令和7年度</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>令和8年度</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>令和12年度</t>
         </is>
       </c>
-      <c r="K47" s="4" t="inlineStr">
+      <c r="L47" s="4" t="inlineStr">
         <is>
           <t>令和17年度</t>
         </is>
       </c>
-      <c r="L47" s="4" t="inlineStr">
+      <c r="M47" s="4" t="inlineStr">
         <is>
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="M47" s="4" t="inlineStr">
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>令和27年度</t>
         </is>
       </c>
-      <c r="N47" s="4" t="inlineStr">
+      <c r="O47" s="4" t="inlineStr">
         <is>
           <t>令和32年度</t>
         </is>
@@ -2287,10 +2479,14 @@
       </c>
       <c r="C48" s="35" t="inlineStr">
         <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D48" s="35" t="inlineStr">
+        <is>
           <t>システムが計算します</t>
         </is>
       </c>
-      <c r="D48" s="36" t="inlineStr"/>
       <c r="E48" s="36" t="inlineStr"/>
       <c r="F48" s="36" t="inlineStr"/>
       <c r="G48" s="36" t="inlineStr"/>
@@ -2301,6 +2497,7 @@
       <c r="L48" s="36" t="inlineStr"/>
       <c r="M48" s="36" t="inlineStr"/>
       <c r="N48" s="36" t="inlineStr"/>
+      <c r="O48" s="36" t="inlineStr"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="35" t="inlineStr"/>
@@ -2311,10 +2508,14 @@
       </c>
       <c r="C49" s="35" t="inlineStr">
         <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D49" s="35" t="inlineStr">
+        <is>
           <t>システムが計算します</t>
         </is>
       </c>
-      <c r="D49" s="36" t="inlineStr"/>
       <c r="E49" s="36" t="inlineStr"/>
       <c r="F49" s="36" t="inlineStr"/>
       <c r="G49" s="36" t="inlineStr"/>
@@ -2325,6 +2526,7 @@
       <c r="L49" s="36" t="inlineStr"/>
       <c r="M49" s="36" t="inlineStr"/>
       <c r="N49" s="36" t="inlineStr"/>
+      <c r="O49" s="36" t="inlineStr"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="35" t="inlineStr"/>
@@ -2335,10 +2537,14 @@
       </c>
       <c r="C50" s="35" t="inlineStr">
         <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D50" s="35" t="inlineStr">
+        <is>
           <t>システムが計算します</t>
         </is>
       </c>
-      <c r="D50" s="36" t="inlineStr"/>
       <c r="E50" s="36" t="inlineStr"/>
       <c r="F50" s="36" t="inlineStr"/>
       <c r="G50" s="36" t="inlineStr"/>
@@ -2349,6 +2555,7 @@
       <c r="L50" s="36" t="inlineStr"/>
       <c r="M50" s="36" t="inlineStr"/>
       <c r="N50" s="36" t="inlineStr"/>
+      <c r="O50" s="36" t="inlineStr"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="35" t="inlineStr"/>
@@ -2359,10 +2566,14 @@
       </c>
       <c r="C51" s="35" t="inlineStr">
         <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D51" s="35" t="inlineStr">
+        <is>
           <t>システムが計算します</t>
         </is>
       </c>
-      <c r="D51" s="36" t="inlineStr"/>
       <c r="E51" s="36" t="inlineStr"/>
       <c r="F51" s="36" t="inlineStr"/>
       <c r="G51" s="36" t="inlineStr"/>
@@ -2373,6 +2584,7 @@
       <c r="L51" s="36" t="inlineStr"/>
       <c r="M51" s="36" t="inlineStr"/>
       <c r="N51" s="36" t="inlineStr"/>
+      <c r="O51" s="36" t="inlineStr"/>
     </row>
     <row r="52" ht="104" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
@@ -2398,25 +2610,29 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr"/>
       <c r="I55" s="4" t="inlineStr"/>
       <c r="J55" s="4" t="inlineStr"/>
@@ -2424,6 +2640,7 @@
       <c r="L55" s="4" t="inlineStr"/>
       <c r="M55" s="4" t="inlineStr"/>
       <c r="N55" s="4" t="inlineStr"/>
+      <c r="O55" s="4" t="inlineStr"/>
     </row>
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="5" t="n">
@@ -2436,11 +2653,13 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
+          <t>手順8</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
-      </c>
-      <c r="D56" s="14" t="n">
-        <v>107129318</v>
       </c>
       <c r="E56" s="14" t="n">
         <v>107129318</v>
@@ -2448,7 +2667,9 @@
       <c r="F56" s="14" t="n">
         <v>107129318</v>
       </c>
-      <c r="G56" s="5" t="inlineStr"/>
+      <c r="G56" s="14" t="n">
+        <v>107129318</v>
+      </c>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="5" t="inlineStr"/>
@@ -2456,6 +2677,7 @@
       <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr"/>
       <c r="N56" s="5" t="inlineStr"/>
+      <c r="O56" s="5" t="inlineStr"/>
     </row>
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="5" t="n">
@@ -2468,11 +2690,13 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
+          <t>手順8</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
-      </c>
-      <c r="D57" s="14" t="n">
-        <v>70031941</v>
       </c>
       <c r="E57" s="14" t="n">
         <v>70031941</v>
@@ -2480,7 +2704,9 @@
       <c r="F57" s="14" t="n">
         <v>70031941</v>
       </c>
-      <c r="G57" s="5" t="inlineStr"/>
+      <c r="G57" s="14" t="n">
+        <v>70031941</v>
+      </c>
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr"/>
@@ -2488,6 +2714,7 @@
       <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr"/>
       <c r="N57" s="5" t="inlineStr"/>
+      <c r="O57" s="5" t="inlineStr"/>
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="8" t="n">
@@ -2500,11 +2727,13 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
+          <t>手順8</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
           <t>事業費（円）</t>
         </is>
-      </c>
-      <c r="D58" s="10" t="n">
-        <v>177161259</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>177161259</v>
@@ -2512,7 +2741,9 @@
       <c r="F58" s="10" t="n">
         <v>177161259</v>
       </c>
-      <c r="G58" s="8" t="inlineStr"/>
+      <c r="G58" s="10" t="n">
+        <v>177161259</v>
+      </c>
       <c r="H58" s="8" t="inlineStr"/>
       <c r="I58" s="8" t="inlineStr"/>
       <c r="J58" s="8" t="inlineStr"/>
@@ -2520,6 +2751,7 @@
       <c r="L58" s="8" t="inlineStr"/>
       <c r="M58" s="8" t="inlineStr"/>
       <c r="N58" s="8" t="inlineStr"/>
+      <c r="O58" s="8" t="inlineStr"/>
     </row>
     <row r="59" ht="32" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
@@ -2530,16 +2762,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A6:N6"/>
-    <mergeCell ref="A34:N34"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A38:N38"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A54:N54"/>
+    <mergeCell ref="A59:O59"/>
+    <mergeCell ref="A38:O38"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A54:O54"/>
     <mergeCell ref="A52:N52"/>
-    <mergeCell ref="A59:N59"/>
-    <mergeCell ref="A46:N46"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A46:O46"/>
+    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A34:O34"/>
+    <mergeCell ref="A4:O4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/output/第10期計画_見える化_入力箇所と入力値.xlsx
+++ b/output/第10期計画_見える化_入力箇所と入力値.xlsx
@@ -246,11 +246,11 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -653,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -771,7 +771,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>施設・居住系・在宅・地域支援事業は入力の様式が違います。施設・居住系は利用者数（人）、在宅は利用率（％）、地域支援事業は量（人）と事業費（円）が同じ表に並びます。本表は画面ごとの様式に合わせて分けています。</t>
+          <t>施設・居住系・在宅・利用回（日）数・地域支援事業は入力の様式が違います。施設・居住系は利用者数（人）、在宅は利用率（％）、利用回（日）数は1人1月あたりの回（日）数、地域支援事業は量（人）と事業費（円）です。本表は画面ごとの様式に合わせて分けています。</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>「―」の意味</t>
+          <t>同じ「回（日）数」でも画面により意味が違うこと</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>制度上その要介護度の区分がないもの（画面に列がないもの）です。0とは意味が違います。0は「区分はあるが計上がない」ことを表します。</t>
+          <t>手順5の施策反映の画面に入れるのは1人1月あたりの回（日）数です（08シート）。手順2の令和8年度の実績見込み値の欄に入れるのは1月当たりの延べの回（日）数です（04シート）。延べの値を施策反映の画面に入れると桁が大きく違います。</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>入れる値の色</t>
+          <t>「―」の意味</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>黄色の欄が入力する値です。灰色は実績・参考であり入力しません。</t>
+          <t>制度上その要介護度の区分がないもの（画面に列がないもの）です。0とは意味が違います。0は「区分はあるが計上がない」ことを表します。</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>暫定値であること</t>
+          <t>入れる値の色</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。　必要資料が届いたとき、及び国の告示・政令が示されたときに置き直します。</t>
+          <t>黄色の欄が入力する値です。灰色は実績・参考であり入力しません。</t>
         </is>
       </c>
     </row>
@@ -826,237 +826,252 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
+          <t>暫定値であること</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。　必要資料が届いたとき、及び国の告示・政令が示されたときに置き直します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
           <t>入力後の確かめ方</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>12シートに、入力が正しく効いたかどうかを確かめる値を掲げています。</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="16"/>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>2　シートの構成</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>シート</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>画面（手順）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>01_変更する箇所の一覧</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>全体</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>02_人口の設定</t>
+          <t>01_変更する箇所の一覧</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>手順2　実績及び推計方法の設定／総人口と被保険者数の設定</t>
+          <t>全体</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>03_設定の選択</t>
+          <t>02_人口の設定</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>手順2から手順5　推計方法の設定で選ぶ項目</t>
+          <t>手順2　実績及び推計方法の設定／総人口と被保険者数の設定</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>04_令和8年度の実績見込み値</t>
+          <t>03_設定の選択</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>手順2　実績及び推計方法の設定／令和8年度の実績見込み値</t>
+          <t>手順2から手順5　推計方法の設定で選ぶ項目</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>05_認定者数</t>
+          <t>04_令和8年度の実績見込み値</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>手順3　施策反映　認定者数</t>
+          <t>手順2　実績及び推計方法の設定／令和8年度の実績見込み値</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>06_施設居住系の利用者数</t>
+          <t>05_認定者数</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>手順4　施策反映　施設・居住系サービス利用者数</t>
+          <t>手順3　施策反映　認定者数</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>07_在宅の利用率と利用者数</t>
+          <t>06_施設居住系の利用者数</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>手順5　施策反映　在宅サービス利用者数（利用率）</t>
+          <t>手順4　施策反映　施設・居住系サービス利用者数</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>08_在宅の利用回日数</t>
+          <t>07_在宅の利用率と利用者数</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>手順5　施策反映　在宅サービス利用回（日）数</t>
+          <t>手順5　施策反映　在宅サービス利用者数（利用率）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>09_地域支援事業の量</t>
+          <t>08_在宅の利用回日数</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>手順6　地域支援事業の見込み量推計</t>
+          <t>手順5　施策反映　在宅サービス利用回（日）数</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10_地域支援事業費</t>
+          <t>09_地域支援事業の量</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>手順7　地域支援事業費</t>
+          <t>手順6　地域支援事業の見込み量推計</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>11_保険料額の算定</t>
+          <t>10_地域支援事業費</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>手順8　保険料額の算定</t>
+          <t>手順7　地域支援事業費</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>12_入力後の確かめ方</t>
+          <t>11_保険料額の算定</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>推計結果概要の確認</t>
+          <t>手順8　保険料額の算定</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>12_入力後の確かめ方</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>推計結果概要の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>13_自己点検</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="40" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>注）本表は入力する値を示すものであり、画面の操作の手引ではありません。操作の手引と認証後の画面の一覧は受領していないため、画面の項目名は受領した画面の写しによっています（確認事項No.148）。</t>
         </is>
@@ -1065,10 +1080,10 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1124,7 +1139,7 @@
     </row>
     <row r="3"/>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>【この画面の値は特に暫定の度合いが高いものです】
 総合事業の令和7年度実績が未受領であるため、令和6年度の利用者実人数（3町計）を基準として据え置き、認定者数の伸びで延ばしています（確認事項No.112）。
@@ -1222,11 +1237,11 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="31" t="n">
         <v>75</v>
       </c>
-      <c r="E8" s="30" t="inlineStr"/>
-      <c r="F8" s="30" t="inlineStr"/>
+      <c r="E8" s="31" t="inlineStr"/>
+      <c r="F8" s="31" t="inlineStr"/>
       <c r="G8" s="24" t="n">
         <v>76.59999999999999</v>
       </c>
@@ -1282,11 +1297,11 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="E10" s="30" t="inlineStr"/>
-      <c r="F10" s="30" t="inlineStr"/>
+      <c r="E10" s="31" t="inlineStr"/>
+      <c r="F10" s="31" t="inlineStr"/>
       <c r="G10" s="24" t="n">
         <v>40.8</v>
       </c>
@@ -1316,11 +1331,11 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="31" t="n">
         <v>149</v>
       </c>
-      <c r="E11" s="30" t="inlineStr"/>
-      <c r="F11" s="30" t="inlineStr"/>
+      <c r="E11" s="31" t="inlineStr"/>
+      <c r="F11" s="31" t="inlineStr"/>
       <c r="G11" s="24" t="n">
         <v>152.1</v>
       </c>
@@ -1786,7 +1801,7 @@
     </row>
     <row r="3"/>
     <row r="4" ht="56" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>【この画面の値は特に暫定の度合いが高いものです】
 事業別の内訳（総合事業23項目・包括的支援事業8項目）は未受領です（確認事項No.5・No.112・No.150）。当広域連合が用意できるのは総合事業費の計と包括的支援事業・任意事業費の計の2つだけであり、事業別に割り付けられません。
@@ -4074,7 +4089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4443,8 +4458,33 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="62" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>利用回（日）数（延べ・令和11年度）</t>
+        </is>
+      </c>
+      <c r="C20" s="42" t="inlineStr">
+        <is>
+          <t>計画本文は20,927.6回・日／月</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>本表の入力から 20,942.4回・日／月</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>画面は1人1月あたりを要介護度別に入れるため、システムが求める延べは要介護度の構成の動きを取り込みます。計画本文は要支援・要介護の群でまとめた1人1月あたりによっており、差は最大 +0.09％（訪問介護）です。保険料には入りません</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="62" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>注1）本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。
 注2）算定式そのものは当方と見える化で同じです。第9期の保険料基準額は見える化6427.89円・当方の再現6,427.92円で一致しており、差は入力と設定によるものです。
@@ -4454,9 +4494,9 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A14:E14"/>
   </mergeCells>
@@ -4479,7 +4519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4816,12 +4856,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>04・05・06・07・08シートの全行を読み直して検算（合計の欄は画面と同じく左端。従前の右端の「計」も拾う）</t>
+          <t>04・05・06・07シートの全行を読み直して検算（合計の欄は画面と同じく左端。従前の右端の「計」も拾う）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>404行を検算／合わない なし</t>
+          <t>296行を検算（04 35・05 9・06 63・07 189）／合わない なし／数えられていないシート なし</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -5105,27 +5145,102 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="8" t="inlineStr"/>
-      <c r="B28" s="8" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>利用回（日）数の画面の区分が当方の回（日）数の区分と一致すること</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>画面のプルダウン ＝ 回（日）数の計上がある区分</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>画面12区分・当方12区分／差 なし</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>利用回（日）数の表に合計の列を置いていないこと</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>画面に合計の列がない（見出しと値の行の両方を見る）</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>見出し11列（サービス（プルダウンで選ぶ）・単位・年度・要支援1・要支援2・要介護1・要介護2・要介護3・要介護4・要介護5）／見出しより右に値のある行 なし</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度の1人1月あたりが画面の表示値と一致すること</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>画面の写し（訪問介護・訪問看護）と当方の年報の要介護度別明細による算定</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>2区分・12欄／合わない なし</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="8" t="inlineStr"/>
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>自己点検の結果</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>適合23件・不適合0件</t>
-        </is>
-      </c>
-      <c r="E28" s="43" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>適合26件・不適合0件</t>
+        </is>
+      </c>
+      <c r="E31" s="43" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>注）本シートは点検の記録であり、本表の値が暫定値であることを変えるものではありません。</t>
         </is>
@@ -5134,8 +5249,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A32:E32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -5848,7 +5963,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>小数第1位まで</t>
+          <t>別画面。入れるのは1人1月あたり（延べではない）。小数第1位まで</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
@@ -9363,7 +9478,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>4　在宅サービス利用回（日）数（回・日／月）</t>
+          <t>4　在宅サービス利用回（日）数（1月当たりの延べ・回・日）</t>
         </is>
       </c>
     </row>
@@ -9810,14 +9925,15 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="51" ht="74" customHeight="1">
+    <row r="51" ht="96" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
           <t>注1）本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。
 注2）出所は年報 令和7年度（確定値・要介護度別）です。
 注3）人数の欄は整数で扱われるため整数で掲げています。要支援の群・要介護の群ごとに合計を保つよう配分しているため、月1人に満たないサービスも0にはなりません。
 注4）「―」は制度上その要介護度の区分がないものです。
-注5）認知症対応型共同生活介護の要支援2（月0.42人）のように、月1人に満たない区分は整数の欄では0になります。システムのワーニングチェックで挙がりますが、整数の欄である以上ほかに置きようがないため、理由の記入で足ります。</t>
+注5）認知症対応型共同生活介護の要支援2（月0.42人）のように、月1人に満たない区分は整数の欄では0になります。システムのワーニングチェックで挙がりますが、整数の欄である以上ほかに置きようがないため、理由の記入で足ります。
+注6）4の回（日）数は1月当たりの延べです。手順5の施策反映の画面（08シート）に入れるのは1人1月あたりの回（日）数であり、同じ「回（日）数」でも画面により意味が違います。本表の値は年報の年間延べを12で除したもので、3の利用者数で除した1人1月あたりが総括表詳細（３）と3％以内で一致することを確かめています。</t>
         </is>
       </c>
     </row>
@@ -25923,21 +26039,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L116"/>
+  <dimension ref="A1:K118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -25950,199 +26065,125 @@
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>【暫定値】　本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。　在宅サービスの画面の「利用回（日）数の施策反映へ」から開く画面に入れる値です。1月当たりの延べ回（日）数であり、1人1月あたりではありません。利用回（日）数の欄は小数第1位まで受け付けます。1人1月あたり回（日）数を令和7年度で固定し、利用者数に乗じています。</t>
+          <t>【暫定値】　本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。　画面はサービスのプルダウンで1サービスにつき1つ開きます。入れるのは1人1月あたりの回（日）数であり、1月当たりの延べ回（日）数ではありません。画面に合計の列はありません（列は要支援1・要支援2・要介護1〜5の7つだけです）。欄は小数第1位まで受け付けます。</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>（１）居宅サービス　利用回（日）数（回・日／月・小数第1位）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>サービス</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>【画面の説明文（逐語）】
+自然体推計された在宅サービスの利用回(日)数について、令和9年度以降に施策の効果として見込まれる値を入力してください。
+プルダウンに並ぶのは回（日）数の計上がある12区分だけです（居宅療養管理指導・福祉用具貸与・月包括報酬によるものは並びません）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>（１）居宅サービス　【入力】1人1月あたりの利用回（日）数（回・日／月・小数第1位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>サービス（プルダウンで選ぶ）</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>年度</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>要支援1</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>要支援2</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>要介護1</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>要介護2</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>要介護3</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>要介護4</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>要介護5</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="n">
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>訪問介護</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>回</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>令和7年度
 （実績）</t>
         </is>
       </c>
-      <c r="E6" s="30" t="n">
-        <v>14965.1</v>
-      </c>
-      <c r="F6" s="25" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G6" s="25" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="H6" s="25" t="n">
-        <v>5536.3</v>
-      </c>
-      <c r="I6" s="25" t="n">
-        <v>2752</v>
-      </c>
-      <c r="J6" s="25" t="n">
-        <v>2359.5</v>
-      </c>
-      <c r="K6" s="25" t="n">
-        <v>2461.1</v>
-      </c>
-      <c r="L6" s="25" t="n">
-        <v>1856.2</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="n">
-        <v>15285.4</v>
-      </c>
-      <c r="F7" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G7" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="H7" s="24" t="n">
-        <v>5644.6</v>
-      </c>
-      <c r="I7" s="24" t="n">
-        <v>2813.1</v>
-      </c>
-      <c r="J7" s="24" t="n">
-        <v>2416.3</v>
-      </c>
-      <c r="K7" s="24" t="n">
-        <v>2518</v>
-      </c>
-      <c r="L7" s="24" t="n">
-        <v>1893.4</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="E8" s="25" t="n">
-        <v>15449.3</v>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G8" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="H8" s="24" t="n">
-        <v>5700.1</v>
-      </c>
-      <c r="I8" s="24" t="n">
-        <v>2844.3</v>
-      </c>
-      <c r="J8" s="24" t="n">
-        <v>2445.4</v>
-      </c>
-      <c r="K8" s="24" t="n">
-        <v>2547</v>
-      </c>
-      <c r="L8" s="24" t="n">
-        <v>1912.5</v>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F8" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H8" s="25" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="I8" s="25" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="J8" s="25" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="K8" s="25" t="n">
+        <v>113.2</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -26151,36 +26192,33 @@
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="E9" s="25" t="n">
-        <v>15615.7</v>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G9" s="24" t="n">
+        <v>23.6</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>5756.6</v>
+        <v>36.5</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>2876</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J9" s="24" t="n">
-        <v>2474.8</v>
+        <v>92.8</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>2576.5</v>
-      </c>
-      <c r="L9" s="24" t="n">
-        <v>1931.8</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -26189,36 +26227,33 @@
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>令和12年度</t>
-        </is>
-      </c>
-      <c r="E10" s="25" t="n">
-        <v>15734.3</v>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G10" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G10" s="24" t="n">
+        <v>23.6</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>5796.9</v>
+        <v>36.5</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>2898.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J10" s="24" t="n">
-        <v>2495.5</v>
+        <v>92.8</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>2597.6</v>
-      </c>
-      <c r="L10" s="24" t="n">
-        <v>1945.6</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -26227,36 +26262,33 @@
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>令和17年度</t>
-        </is>
-      </c>
-      <c r="E11" s="25" t="n">
-        <v>17003.7</v>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G11" s="24" t="n">
+        <v>23.6</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>6225.1</v>
+        <v>36.5</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>3135.1</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>2730</v>
+        <v>92.8</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>2818.3</v>
-      </c>
-      <c r="L11" s="24" t="n">
-        <v>2095.2</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -26265,36 +26297,33 @@
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>令和22年度</t>
-        </is>
-      </c>
-      <c r="E12" s="25" t="n">
-        <v>17522.5</v>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G12" s="24" t="n">
+        <v>23.6</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>6411</v>
+        <v>36.5</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>3229.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>2819.2</v>
+        <v>92.8</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>2903.9</v>
-      </c>
-      <c r="L12" s="24" t="n">
-        <v>2159.1</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -26303,36 +26332,33 @@
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>令和27年度</t>
-        </is>
-      </c>
-      <c r="E13" s="25" t="n">
-        <v>16743.7</v>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G13" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G13" s="24" t="n">
+        <v>23.6</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>6144</v>
+        <v>36.5</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>3084.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>2679.3</v>
+        <v>92.8</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>2769.5</v>
-      </c>
-      <c r="L13" s="24" t="n">
-        <v>2066.6</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -26341,81 +26367,68 @@
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>令和32年度</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="n">
-        <v>16629.7</v>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G14" s="24" t="n">
+        <v>23.6</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>6095</v>
+        <v>36.5</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>3068</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>2660.9</v>
+        <v>92.8</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>2756.4</v>
-      </c>
-      <c r="L14" s="24" t="n">
-        <v>2049.4</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>訪問入浴介護</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>回</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>令和7年度
-（実績）</t>
-        </is>
-      </c>
-      <c r="E15" s="30" t="n">
-        <v>33</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I15" s="25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J15" s="25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K15" s="25" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="L15" s="25" t="n">
-        <v>15.2</v>
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="I15" s="24" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="J15" s="24" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>113.2</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -26424,66 +26437,79 @@
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="F16" s="24" t="n">
-        <v>0</v>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G16" s="24" t="n">
-        <v>0</v>
+        <v>23.6</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>7.5</v>
+        <v>36.5</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>1.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>1.6</v>
+        <v>92.8</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L16" s="24" t="n">
-        <v>15.5</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="n">
-        <v>34</v>
-      </c>
-      <c r="F17" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I17" s="24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J17" s="24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K17" s="24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L17" s="24" t="n">
-        <v>15.7</v>
+      <c r="A17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>訪問入浴介護</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>令和7年度
+（実績）</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I17" s="25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J17" s="25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K17" s="25" t="n">
+        <v>7.4</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -26492,32 +26518,33 @@
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>0</v>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G18" s="24" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L18" s="24" t="n">
-        <v>15.8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -26526,32 +26553,33 @@
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>令和12年度</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>0</v>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G19" s="24" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>7.7</v>
+        <v>3.7</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J19" s="24" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L19" s="24" t="n">
-        <v>15.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -26560,32 +26588,33 @@
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>令和17年度</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>0</v>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G20" s="24" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>8.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J20" s="24" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L20" s="24" t="n">
-        <v>17.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -26594,32 +26623,33 @@
       <c r="C21" s="5" t="inlineStr"/>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>令和22年度</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="F21" s="24" t="n">
-        <v>0</v>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G21" s="24" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>8.5</v>
+        <v>3.7</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J21" s="24" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L21" s="24" t="n">
-        <v>17.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -26628,32 +26658,33 @@
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>令和27年度</t>
-        </is>
-      </c>
-      <c r="E22" s="25" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="F22" s="24" t="n">
-        <v>0</v>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G22" s="24" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>8.1</v>
+        <v>3.7</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J22" s="24" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L22" s="24" t="n">
-        <v>16.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -26662,77 +26693,68 @@
       <c r="C23" s="5" t="inlineStr"/>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>令和32年度</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="F23" s="24" t="n">
-        <v>0</v>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G23" s="24" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>8.1</v>
+        <v>3.7</v>
       </c>
       <c r="I23" s="24" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J23" s="24" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L23" s="24" t="n">
-        <v>16.8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>訪問看護</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>回</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>令和7年度
-（実績）</t>
-        </is>
-      </c>
-      <c r="E24" s="30" t="n">
-        <v>1076</v>
-      </c>
-      <c r="F24" s="25" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="G24" s="25" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="H24" s="25" t="n">
-        <v>360.7</v>
-      </c>
-      <c r="I24" s="25" t="n">
-        <v>223.2</v>
-      </c>
-      <c r="J24" s="25" t="n">
-        <v>121.4</v>
-      </c>
-      <c r="K24" s="25" t="n">
-        <v>133.2</v>
-      </c>
-      <c r="L24" s="25" t="n">
-        <v>133.9</v>
+      <c r="A24" s="5" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H24" s="24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I24" s="24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J24" s="24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K24" s="24" t="n">
+        <v>7.4</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -26741,66 +26763,75 @@
       <c r="C25" s="5" t="inlineStr"/>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="E25" s="25" t="n">
-        <v>1098.7</v>
-      </c>
-      <c r="F25" s="24" t="n">
-        <v>44.3</v>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G25" s="24" t="n">
-        <v>61.3</v>
+        <v>7.4</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>367.8</v>
+        <v>3.7</v>
       </c>
       <c r="I25" s="24" t="n">
-        <v>228.1</v>
+        <v>3.3</v>
       </c>
       <c r="J25" s="24" t="n">
-        <v>124.4</v>
+        <v>4.1</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>136.2</v>
-      </c>
-      <c r="L25" s="24" t="n">
-        <v>136.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="5" t="inlineStr"/>
-      <c r="B26" s="5" t="inlineStr"/>
-      <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
+      <c r="A26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>訪問看護</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>令和7年度
+（実績）</t>
         </is>
       </c>
       <c r="E26" s="25" t="n">
-        <v>1110.3</v>
-      </c>
-      <c r="F26" s="24" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="G26" s="24" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="H26" s="24" t="n">
-        <v>371.4</v>
-      </c>
-      <c r="I26" s="24" t="n">
-        <v>230.6</v>
-      </c>
-      <c r="J26" s="24" t="n">
-        <v>125.9</v>
-      </c>
-      <c r="K26" s="24" t="n">
-        <v>137.8</v>
-      </c>
-      <c r="L26" s="24" t="n">
-        <v>138</v>
+        <v>3.9</v>
+      </c>
+      <c r="F26" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G26" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="I26" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="K26" s="25" t="n">
+        <v>15.9</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -26809,32 +26840,29 @@
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="n">
-        <v>1122.1</v>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="n">
+        <v>3.9</v>
       </c>
       <c r="F27" s="24" t="n">
-        <v>45.2</v>
+        <v>4.5</v>
       </c>
       <c r="G27" s="24" t="n">
-        <v>62.4</v>
+        <v>6</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>375.1</v>
+        <v>7</v>
       </c>
       <c r="I27" s="24" t="n">
-        <v>233.2</v>
+        <v>8</v>
       </c>
       <c r="J27" s="24" t="n">
-        <v>127.4</v>
+        <v>13</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>139.4</v>
-      </c>
-      <c r="L27" s="24" t="n">
-        <v>139.4</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -26843,32 +26871,29 @@
       <c r="C28" s="5" t="inlineStr"/>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>令和12年度</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="n">
-        <v>1130.5</v>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="n">
+        <v>3.9</v>
       </c>
       <c r="F28" s="24" t="n">
-        <v>45.5</v>
+        <v>4.5</v>
       </c>
       <c r="G28" s="24" t="n">
-        <v>62.9</v>
+        <v>6</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>377.7</v>
+        <v>7</v>
       </c>
       <c r="I28" s="24" t="n">
-        <v>235.1</v>
+        <v>8</v>
       </c>
       <c r="J28" s="24" t="n">
-        <v>128.5</v>
+        <v>13</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>140.5</v>
-      </c>
-      <c r="L28" s="24" t="n">
-        <v>140.3</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -26877,32 +26902,29 @@
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>令和17年度</t>
-        </is>
-      </c>
-      <c r="E29" s="25" t="n">
-        <v>1217.1</v>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="n">
+        <v>3.9</v>
       </c>
       <c r="F29" s="24" t="n">
-        <v>47.4</v>
+        <v>4.5</v>
       </c>
       <c r="G29" s="24" t="n">
-        <v>65.7</v>
+        <v>6</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>405.6</v>
+        <v>7</v>
       </c>
       <c r="I29" s="24" t="n">
-        <v>254.2</v>
+        <v>8</v>
       </c>
       <c r="J29" s="24" t="n">
-        <v>140.5</v>
+        <v>13</v>
       </c>
       <c r="K29" s="24" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="L29" s="24" t="n">
-        <v>151.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -26911,32 +26933,29 @@
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>令和22年度</t>
-        </is>
-      </c>
-      <c r="E30" s="25" t="n">
-        <v>1252.8</v>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="n">
+        <v>3.9</v>
       </c>
       <c r="F30" s="24" t="n">
-        <v>48.3</v>
+        <v>4.5</v>
       </c>
       <c r="G30" s="24" t="n">
-        <v>66.90000000000001</v>
+        <v>6</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>417.7</v>
+        <v>7</v>
       </c>
       <c r="I30" s="24" t="n">
-        <v>261.9</v>
+        <v>8</v>
       </c>
       <c r="J30" s="24" t="n">
-        <v>145.1</v>
+        <v>13</v>
       </c>
       <c r="K30" s="24" t="n">
-        <v>157.1</v>
-      </c>
-      <c r="L30" s="24" t="n">
-        <v>155.8</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -26945,32 +26964,29 @@
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>令和27年度</t>
-        </is>
-      </c>
-      <c r="E31" s="25" t="n">
-        <v>1199</v>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="n">
+        <v>3.9</v>
       </c>
       <c r="F31" s="24" t="n">
-        <v>46.8</v>
+        <v>4.5</v>
       </c>
       <c r="G31" s="24" t="n">
-        <v>64.90000000000001</v>
+        <v>6</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>400.3</v>
+        <v>7</v>
       </c>
       <c r="I31" s="24" t="n">
-        <v>250.1</v>
+        <v>8</v>
       </c>
       <c r="J31" s="24" t="n">
-        <v>137.9</v>
+        <v>13</v>
       </c>
       <c r="K31" s="24" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="L31" s="24" t="n">
-        <v>149.1</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -26979,77 +26995,60 @@
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>令和32年度</t>
-        </is>
-      </c>
-      <c r="E32" s="25" t="n">
-        <v>1192.4</v>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="n">
+        <v>3.9</v>
       </c>
       <c r="F32" s="24" t="n">
-        <v>47.2</v>
+        <v>4.5</v>
       </c>
       <c r="G32" s="24" t="n">
-        <v>65.3</v>
+        <v>6</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>397.1</v>
+        <v>7</v>
       </c>
       <c r="I32" s="24" t="n">
-        <v>248.8</v>
+        <v>8</v>
       </c>
       <c r="J32" s="24" t="n">
-        <v>137</v>
+        <v>13</v>
       </c>
       <c r="K32" s="24" t="n">
-        <v>149.2</v>
-      </c>
-      <c r="L32" s="24" t="n">
-        <v>147.8</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>訪問リハビリテーション</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>回</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>令和7年度
-（実績）</t>
-        </is>
-      </c>
-      <c r="E33" s="30" t="n">
-        <v>764.6</v>
-      </c>
-      <c r="F33" s="25" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="G33" s="25" t="n">
-        <v>107.4</v>
-      </c>
-      <c r="H33" s="25" t="n">
-        <v>236.7</v>
-      </c>
-      <c r="I33" s="25" t="n">
-        <v>196.7</v>
-      </c>
-      <c r="J33" s="25" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="K33" s="25" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="L33" s="25" t="n">
-        <v>54.5</v>
+      <c r="A33" s="5" t="inlineStr"/>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F33" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G33" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="I33" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="J33" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="K33" s="24" t="n">
+        <v>15.9</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -27058,66 +27057,71 @@
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="E34" s="25" t="n">
-        <v>780.7</v>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="n">
+        <v>3.9</v>
       </c>
       <c r="F34" s="24" t="n">
-        <v>33.5</v>
+        <v>4.5</v>
       </c>
       <c r="G34" s="24" t="n">
-        <v>109.5</v>
+        <v>6</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>241.3</v>
+        <v>7</v>
       </c>
       <c r="I34" s="24" t="n">
-        <v>201.1</v>
+        <v>8</v>
       </c>
       <c r="J34" s="24" t="n">
-        <v>93.8</v>
+        <v>13</v>
       </c>
       <c r="K34" s="24" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="L34" s="24" t="n">
-        <v>55.6</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="5" t="inlineStr"/>
-      <c r="B35" s="5" t="inlineStr"/>
-      <c r="C35" s="5" t="inlineStr"/>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
+      <c r="A35" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>訪問リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>令和7年度
+（実績）</t>
         </is>
       </c>
       <c r="E35" s="25" t="n">
-        <v>788.9</v>
-      </c>
-      <c r="F35" s="24" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="G35" s="24" t="n">
-        <v>110.5</v>
-      </c>
-      <c r="H35" s="24" t="n">
-        <v>243.7</v>
-      </c>
-      <c r="I35" s="24" t="n">
-        <v>203.3</v>
-      </c>
-      <c r="J35" s="24" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="K35" s="24" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="L35" s="24" t="n">
-        <v>56.2</v>
+        <v>7.6</v>
+      </c>
+      <c r="F35" s="25" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G35" s="25" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H35" s="25" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="I35" s="25" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J35" s="25" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K35" s="25" t="n">
+        <v>12.2</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -27126,32 +27130,29 @@
       <c r="C36" s="5" t="inlineStr"/>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="E36" s="25" t="n">
-        <v>797.2</v>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="n">
+        <v>7.6</v>
       </c>
       <c r="F36" s="24" t="n">
-        <v>34.2</v>
+        <v>11.3</v>
       </c>
       <c r="G36" s="24" t="n">
-        <v>111.6</v>
+        <v>10.3</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>246.1</v>
+        <v>12.4</v>
       </c>
       <c r="I36" s="24" t="n">
-        <v>205.6</v>
+        <v>14.2</v>
       </c>
       <c r="J36" s="24" t="n">
-        <v>96</v>
+        <v>10.3</v>
       </c>
       <c r="K36" s="24" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="L36" s="24" t="n">
-        <v>56.8</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -27160,32 +27161,29 @@
       <c r="C37" s="5" t="inlineStr"/>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>令和12年度</t>
-        </is>
-      </c>
-      <c r="E37" s="25" t="n">
-        <v>803.3</v>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="n">
+        <v>7.6</v>
       </c>
       <c r="F37" s="24" t="n">
-        <v>34.4</v>
+        <v>11.3</v>
       </c>
       <c r="G37" s="24" t="n">
-        <v>112.5</v>
+        <v>10.3</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>247.8</v>
+        <v>12.4</v>
       </c>
       <c r="I37" s="24" t="n">
-        <v>207.3</v>
+        <v>14.2</v>
       </c>
       <c r="J37" s="24" t="n">
-        <v>96.8</v>
+        <v>10.3</v>
       </c>
       <c r="K37" s="24" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="L37" s="24" t="n">
-        <v>57.2</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -27194,32 +27192,29 @@
       <c r="C38" s="5" t="inlineStr"/>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>令和17年度</t>
-        </is>
-      </c>
-      <c r="E38" s="25" t="n">
-        <v>862.4</v>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="n">
+        <v>7.6</v>
       </c>
       <c r="F38" s="24" t="n">
-        <v>35.9</v>
+        <v>11.3</v>
       </c>
       <c r="G38" s="24" t="n">
-        <v>117.4</v>
+        <v>10.3</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>266.1</v>
+        <v>12.4</v>
       </c>
       <c r="I38" s="24" t="n">
-        <v>224.2</v>
+        <v>14.2</v>
       </c>
       <c r="J38" s="24" t="n">
-        <v>105.9</v>
+        <v>10.3</v>
       </c>
       <c r="K38" s="24" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="L38" s="24" t="n">
-        <v>61.6</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -27228,32 +27223,29 @@
       <c r="C39" s="5" t="inlineStr"/>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>令和22年度</t>
-        </is>
-      </c>
-      <c r="E39" s="25" t="n">
-        <v>886.8</v>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="n">
+        <v>7.6</v>
       </c>
       <c r="F39" s="24" t="n">
-        <v>36.5</v>
+        <v>11.3</v>
       </c>
       <c r="G39" s="24" t="n">
-        <v>119.6</v>
+        <v>10.3</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>274.1</v>
+        <v>12.4</v>
       </c>
       <c r="I39" s="24" t="n">
-        <v>230.9</v>
+        <v>14.2</v>
       </c>
       <c r="J39" s="24" t="n">
-        <v>109.4</v>
+        <v>10.3</v>
       </c>
       <c r="K39" s="24" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="L39" s="24" t="n">
-        <v>63.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -27262,32 +27254,29 @@
       <c r="C40" s="5" t="inlineStr"/>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>令和27年度</t>
-        </is>
-      </c>
-      <c r="E40" s="25" t="n">
-        <v>849.7</v>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="n">
+        <v>7.6</v>
       </c>
       <c r="F40" s="24" t="n">
-        <v>35.5</v>
+        <v>11.3</v>
       </c>
       <c r="G40" s="24" t="n">
-        <v>115.9</v>
+        <v>10.3</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>262.7</v>
+        <v>12.4</v>
       </c>
       <c r="I40" s="24" t="n">
-        <v>220.5</v>
+        <v>14.2</v>
       </c>
       <c r="J40" s="24" t="n">
-        <v>104</v>
+        <v>10.3</v>
       </c>
       <c r="K40" s="24" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="L40" s="24" t="n">
-        <v>60.7</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -27296,81 +27285,60 @@
       <c r="C41" s="5" t="inlineStr"/>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>令和32年度</t>
-        </is>
-      </c>
-      <c r="E41" s="25" t="n">
-        <v>846.1</v>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="n">
+        <v>7.6</v>
       </c>
       <c r="F41" s="24" t="n">
-        <v>35.7</v>
+        <v>11.3</v>
       </c>
       <c r="G41" s="24" t="n">
-        <v>116.8</v>
+        <v>10.3</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>260.6</v>
+        <v>12.4</v>
       </c>
       <c r="I41" s="24" t="n">
-        <v>219.3</v>
+        <v>14.2</v>
       </c>
       <c r="J41" s="24" t="n">
-        <v>103.3</v>
+        <v>10.3</v>
       </c>
       <c r="K41" s="24" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="L41" s="24" t="n">
-        <v>60.2</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>通所介護</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>回</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>令和7年度
-（実績）</t>
-        </is>
-      </c>
-      <c r="E42" s="30" t="n">
-        <v>850.6</v>
-      </c>
-      <c r="F42" s="25" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G42" s="25" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="H42" s="25" t="n">
-        <v>434</v>
-      </c>
-      <c r="I42" s="25" t="n">
-        <v>193</v>
-      </c>
-      <c r="J42" s="25" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="K42" s="25" t="n">
-        <v>102</v>
-      </c>
-      <c r="L42" s="25" t="n">
-        <v>27.7</v>
+      <c r="A42" s="5" t="inlineStr"/>
+      <c r="B42" s="5" t="inlineStr"/>
+      <c r="C42" s="5" t="inlineStr"/>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F42" s="24" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G42" s="24" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H42" s="24" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="I42" s="24" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J42" s="24" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K42" s="24" t="n">
+        <v>12.2</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -27379,74 +27347,75 @@
       <c r="C43" s="5" t="inlineStr"/>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="E43" s="25" t="n">
-        <v>868.5</v>
-      </c>
-      <c r="F43" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G43" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F43" s="24" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G43" s="24" t="n">
+        <v>10.3</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>442.5</v>
+        <v>12.4</v>
       </c>
       <c r="I43" s="24" t="n">
-        <v>197.3</v>
+        <v>14.2</v>
       </c>
       <c r="J43" s="24" t="n">
-        <v>96.2</v>
+        <v>10.3</v>
       </c>
       <c r="K43" s="24" t="n">
-        <v>104.3</v>
-      </c>
-      <c r="L43" s="24" t="n">
-        <v>28.2</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="5" t="inlineStr"/>
-      <c r="B44" s="5" t="inlineStr"/>
-      <c r="C44" s="5" t="inlineStr"/>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="E44" s="25" t="n">
-        <v>877.7</v>
-      </c>
-      <c r="F44" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G44" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="H44" s="24" t="n">
-        <v>446.9</v>
-      </c>
-      <c r="I44" s="24" t="n">
-        <v>199.4</v>
-      </c>
-      <c r="J44" s="24" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="K44" s="24" t="n">
-        <v>105.5</v>
-      </c>
-      <c r="L44" s="24" t="n">
-        <v>28.5</v>
+      <c r="A44" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>通所介護</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>令和7年度
+（実績）</t>
+        </is>
+      </c>
+      <c r="E44" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F44" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G44" s="25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H44" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I44" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="J44" s="25" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K44" s="25" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -27455,36 +27424,33 @@
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="E45" s="25" t="n">
-        <v>887</v>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G45" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G45" s="24" t="n">
+        <v>8.4</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>451.3</v>
+        <v>7.5</v>
       </c>
       <c r="I45" s="24" t="n">
-        <v>201.7</v>
+        <v>10</v>
       </c>
       <c r="J45" s="24" t="n">
-        <v>98.5</v>
+        <v>11.2</v>
       </c>
       <c r="K45" s="24" t="n">
-        <v>106.7</v>
-      </c>
-      <c r="L45" s="24" t="n">
-        <v>28.8</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -27493,36 +27459,33 @@
       <c r="C46" s="5" t="inlineStr"/>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>令和12年度</t>
-        </is>
-      </c>
-      <c r="E46" s="25" t="n">
-        <v>893.7</v>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G46" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G46" s="24" t="n">
+        <v>8.4</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>454.4</v>
+        <v>7.5</v>
       </c>
       <c r="I46" s="24" t="n">
-        <v>203.3</v>
+        <v>10</v>
       </c>
       <c r="J46" s="24" t="n">
-        <v>99.40000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="K46" s="24" t="n">
-        <v>107.6</v>
-      </c>
-      <c r="L46" s="24" t="n">
-        <v>29</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -27531,36 +27494,33 @@
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>令和17年度</t>
-        </is>
-      </c>
-      <c r="E47" s="25" t="n">
-        <v>964.6</v>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G47" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G47" s="24" t="n">
+        <v>8.4</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>488</v>
+        <v>7.5</v>
       </c>
       <c r="I47" s="24" t="n">
-        <v>219.9</v>
+        <v>10</v>
       </c>
       <c r="J47" s="24" t="n">
-        <v>108.7</v>
+        <v>11.2</v>
       </c>
       <c r="K47" s="24" t="n">
-        <v>116.8</v>
-      </c>
-      <c r="L47" s="24" t="n">
-        <v>31.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -27569,36 +27529,33 @@
       <c r="C48" s="5" t="inlineStr"/>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>令和22年度</t>
-        </is>
-      </c>
-      <c r="E48" s="25" t="n">
-        <v>993.8</v>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G48" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G48" s="24" t="n">
+        <v>8.4</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>502.6</v>
+        <v>7.5</v>
       </c>
       <c r="I48" s="24" t="n">
-        <v>226.5</v>
+        <v>10</v>
       </c>
       <c r="J48" s="24" t="n">
-        <v>112.2</v>
+        <v>11.2</v>
       </c>
       <c r="K48" s="24" t="n">
-        <v>120.3</v>
-      </c>
-      <c r="L48" s="24" t="n">
-        <v>32.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -27607,36 +27564,33 @@
       <c r="C49" s="5" t="inlineStr"/>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>令和27年度</t>
-        </is>
-      </c>
-      <c r="E49" s="25" t="n">
-        <v>950.2</v>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G49" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G49" s="24" t="n">
+        <v>8.4</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>481.7</v>
+        <v>7.5</v>
       </c>
       <c r="I49" s="24" t="n">
-        <v>216.3</v>
+        <v>10</v>
       </c>
       <c r="J49" s="24" t="n">
-        <v>106.7</v>
+        <v>11.2</v>
       </c>
       <c r="K49" s="24" t="n">
-        <v>114.7</v>
-      </c>
-      <c r="L49" s="24" t="n">
-        <v>30.8</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -27645,81 +27599,68 @@
       <c r="C50" s="5" t="inlineStr"/>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>令和32年度</t>
-        </is>
-      </c>
-      <c r="E50" s="25" t="n">
-        <v>943.7</v>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G50" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G50" s="24" t="n">
+        <v>8.4</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>477.8</v>
+        <v>7.5</v>
       </c>
       <c r="I50" s="24" t="n">
-        <v>215.2</v>
+        <v>10</v>
       </c>
       <c r="J50" s="24" t="n">
-        <v>105.9</v>
+        <v>11.2</v>
       </c>
       <c r="K50" s="24" t="n">
-        <v>114.2</v>
-      </c>
-      <c r="L50" s="24" t="n">
-        <v>30.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>通所リハビリテーション</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>回</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>令和7年度
-（実績）</t>
-        </is>
-      </c>
-      <c r="E51" s="30" t="n">
-        <v>1354</v>
-      </c>
-      <c r="F51" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="25" t="n">
-        <v>697.2</v>
-      </c>
-      <c r="I51" s="25" t="n">
-        <v>370.3</v>
-      </c>
-      <c r="J51" s="25" t="n">
-        <v>142.7</v>
-      </c>
-      <c r="K51" s="25" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="L51" s="25" t="n">
-        <v>47.5</v>
+      <c r="A51" s="5" t="inlineStr"/>
+      <c r="B51" s="5" t="inlineStr"/>
+      <c r="C51" s="5" t="inlineStr"/>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H51" s="24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I51" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="J51" s="24" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K51" s="24" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -27728,66 +27669,75 @@
       <c r="C52" s="5" t="inlineStr"/>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="E52" s="25" t="n">
-        <v>1382.5</v>
-      </c>
-      <c r="F52" s="24" t="n">
-        <v>0</v>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G52" s="24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>710.9</v>
+        <v>7.5</v>
       </c>
       <c r="I52" s="24" t="n">
-        <v>378.5</v>
+        <v>10</v>
       </c>
       <c r="J52" s="24" t="n">
-        <v>146.1</v>
+        <v>11.2</v>
       </c>
       <c r="K52" s="24" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="L52" s="24" t="n">
-        <v>48.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="5" t="inlineStr"/>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="5" t="inlineStr"/>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
+      <c r="A53" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>通所リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>令和7年度
+（実績）</t>
         </is>
       </c>
       <c r="E53" s="25" t="n">
-        <v>1397.1</v>
-      </c>
-      <c r="F53" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="24" t="n">
-        <v>717.9</v>
-      </c>
-      <c r="I53" s="24" t="n">
-        <v>382.7</v>
-      </c>
-      <c r="J53" s="24" t="n">
-        <v>147.8</v>
-      </c>
-      <c r="K53" s="24" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="L53" s="24" t="n">
-        <v>49</v>
+        <v>0</v>
+      </c>
+      <c r="F53" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H53" s="25" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I53" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="J53" s="25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K53" s="25" t="n">
+        <v>6.8</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -27796,32 +27746,29 @@
       <c r="C54" s="5" t="inlineStr"/>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="E54" s="25" t="n">
-        <v>1411.9</v>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E54" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="24" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>725</v>
+        <v>7.7</v>
       </c>
       <c r="I54" s="24" t="n">
-        <v>387</v>
+        <v>8</v>
       </c>
       <c r="J54" s="24" t="n">
-        <v>149.6</v>
+        <v>7.6</v>
       </c>
       <c r="K54" s="24" t="n">
-        <v>100.8</v>
-      </c>
-      <c r="L54" s="24" t="n">
-        <v>49.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -27830,32 +27777,29 @@
       <c r="C55" s="5" t="inlineStr"/>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>令和12年度</t>
-        </is>
-      </c>
-      <c r="E55" s="25" t="n">
-        <v>1422.4</v>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E55" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="24" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>730</v>
+        <v>7.7</v>
       </c>
       <c r="I55" s="24" t="n">
-        <v>390.1</v>
+        <v>8</v>
       </c>
       <c r="J55" s="24" t="n">
-        <v>150.9</v>
+        <v>7.6</v>
       </c>
       <c r="K55" s="24" t="n">
-        <v>101.6</v>
-      </c>
-      <c r="L55" s="24" t="n">
-        <v>49.8</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -27864,32 +27808,29 @@
       <c r="C56" s="5" t="inlineStr"/>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>令和17年度</t>
-        </is>
-      </c>
-      <c r="E56" s="25" t="n">
-        <v>1534.8</v>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E56" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="24" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="H56" s="24" t="n">
-        <v>783.9</v>
+        <v>7.7</v>
       </c>
       <c r="I56" s="24" t="n">
-        <v>421.9</v>
+        <v>8</v>
       </c>
       <c r="J56" s="24" t="n">
-        <v>165</v>
+        <v>7.6</v>
       </c>
       <c r="K56" s="24" t="n">
-        <v>110.3</v>
-      </c>
-      <c r="L56" s="24" t="n">
-        <v>53.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -27898,32 +27839,29 @@
       <c r="C57" s="5" t="inlineStr"/>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>令和22年度</t>
-        </is>
-      </c>
-      <c r="E57" s="25" t="n">
-        <v>1581.3</v>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="E57" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="24" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="H57" s="24" t="n">
-        <v>807.4</v>
+        <v>7.7</v>
       </c>
       <c r="I57" s="24" t="n">
-        <v>434.5</v>
+        <v>8</v>
       </c>
       <c r="J57" s="24" t="n">
-        <v>170.5</v>
+        <v>7.6</v>
       </c>
       <c r="K57" s="24" t="n">
-        <v>113.6</v>
-      </c>
-      <c r="L57" s="24" t="n">
-        <v>55.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -27932,32 +27870,29 @@
       <c r="C58" s="5" t="inlineStr"/>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>令和27年度</t>
-        </is>
-      </c>
-      <c r="E58" s="25" t="n">
-        <v>1512</v>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="E58" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="24" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="H58" s="24" t="n">
-        <v>773.7</v>
+        <v>7.7</v>
       </c>
       <c r="I58" s="24" t="n">
-        <v>415</v>
+        <v>8</v>
       </c>
       <c r="J58" s="24" t="n">
-        <v>162</v>
+        <v>7.6</v>
       </c>
       <c r="K58" s="24" t="n">
-        <v>108.4</v>
-      </c>
-      <c r="L58" s="24" t="n">
-        <v>52.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -27966,77 +27901,60 @@
       <c r="C59" s="5" t="inlineStr"/>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>令和32年度</t>
-        </is>
-      </c>
-      <c r="E59" s="25" t="n">
-        <v>1501.6</v>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="E59" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G59" s="24" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="H59" s="24" t="n">
-        <v>767.6</v>
+        <v>7.7</v>
       </c>
       <c r="I59" s="24" t="n">
-        <v>412.8</v>
+        <v>8</v>
       </c>
       <c r="J59" s="24" t="n">
-        <v>160.9</v>
+        <v>7.6</v>
       </c>
       <c r="K59" s="24" t="n">
-        <v>107.8</v>
-      </c>
-      <c r="L59" s="24" t="n">
-        <v>52.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>短期入所生活介護</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>令和7年度
-（実績）</t>
-        </is>
-      </c>
-      <c r="E60" s="30" t="n">
-        <v>306.1</v>
-      </c>
-      <c r="F60" s="25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G60" s="25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H60" s="25" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="I60" s="25" t="n">
-        <v>122.6</v>
-      </c>
-      <c r="J60" s="25" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="K60" s="25" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="L60" s="25" t="n">
-        <v>14.7</v>
+      <c r="A60" s="5" t="inlineStr"/>
+      <c r="B60" s="5" t="inlineStr"/>
+      <c r="C60" s="5" t="inlineStr"/>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="E60" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H60" s="24" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I60" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="J60" s="24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K60" s="24" t="n">
+        <v>6.8</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -28045,66 +27963,71 @@
       <c r="C61" s="5" t="inlineStr"/>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="E61" s="25" t="n">
-        <v>312.8</v>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="E61" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="G61" s="24" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="H61" s="24" t="n">
-        <v>77</v>
+        <v>7.7</v>
       </c>
       <c r="I61" s="24" t="n">
-        <v>125.4</v>
+        <v>8</v>
       </c>
       <c r="J61" s="24" t="n">
-        <v>41.2</v>
+        <v>7.6</v>
       </c>
       <c r="K61" s="24" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="L61" s="24" t="n">
-        <v>15</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="5" t="inlineStr"/>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="5" t="inlineStr"/>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
+      <c r="A62" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>令和7年度
+（実績）</t>
         </is>
       </c>
       <c r="E62" s="25" t="n">
-        <v>316.2</v>
-      </c>
-      <c r="F62" s="24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G62" s="24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H62" s="24" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="I62" s="24" t="n">
-        <v>126.7</v>
-      </c>
-      <c r="J62" s="24" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="K62" s="24" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="L62" s="24" t="n">
-        <v>15.2</v>
+        <v>3.6</v>
+      </c>
+      <c r="F62" s="25" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="G62" s="25" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H62" s="25" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I62" s="25" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J62" s="25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K62" s="25" t="n">
+        <v>11.3</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -28113,32 +28036,29 @@
       <c r="C63" s="5" t="inlineStr"/>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="E63" s="25" t="n">
-        <v>319.7</v>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E63" s="24" t="n">
+        <v>3.6</v>
       </c>
       <c r="F63" s="24" t="n">
-        <v>4.8</v>
+        <v>10.6</v>
       </c>
       <c r="G63" s="24" t="n">
-        <v>7.5</v>
+        <v>11.9</v>
       </c>
       <c r="H63" s="24" t="n">
-        <v>78.59999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="I63" s="24" t="n">
-        <v>128.2</v>
+        <v>16.7</v>
       </c>
       <c r="J63" s="24" t="n">
-        <v>42.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K63" s="24" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="L63" s="24" t="n">
-        <v>15.3</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -28147,32 +28067,29 @@
       <c r="C64" s="5" t="inlineStr"/>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>令和12年度</t>
-        </is>
-      </c>
-      <c r="E64" s="25" t="n">
-        <v>322.1</v>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E64" s="24" t="n">
+        <v>3.6</v>
       </c>
       <c r="F64" s="24" t="n">
-        <v>4.8</v>
+        <v>10.6</v>
       </c>
       <c r="G64" s="24" t="n">
-        <v>7.6</v>
+        <v>11.9</v>
       </c>
       <c r="H64" s="24" t="n">
-        <v>79.09999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="I64" s="24" t="n">
-        <v>129.2</v>
+        <v>16.7</v>
       </c>
       <c r="J64" s="24" t="n">
-        <v>42.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K64" s="24" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="L64" s="24" t="n">
-        <v>15.4</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -28181,32 +28098,29 @@
       <c r="C65" s="5" t="inlineStr"/>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>令和17年度</t>
-        </is>
-      </c>
-      <c r="E65" s="25" t="n">
-        <v>347.9</v>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E65" s="24" t="n">
+        <v>3.6</v>
       </c>
       <c r="F65" s="24" t="n">
-        <v>5</v>
+        <v>10.6</v>
       </c>
       <c r="G65" s="24" t="n">
-        <v>7.9</v>
+        <v>11.9</v>
       </c>
       <c r="H65" s="24" t="n">
-        <v>85</v>
+        <v>10.8</v>
       </c>
       <c r="I65" s="24" t="n">
-        <v>139.7</v>
+        <v>16.7</v>
       </c>
       <c r="J65" s="24" t="n">
-        <v>46.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K65" s="24" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="L65" s="24" t="n">
-        <v>16.6</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -28215,32 +28129,29 @@
       <c r="C66" s="5" t="inlineStr"/>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>令和22年度</t>
-        </is>
-      </c>
-      <c r="E66" s="25" t="n">
-        <v>358.4</v>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="E66" s="24" t="n">
+        <v>3.6</v>
       </c>
       <c r="F66" s="24" t="n">
-        <v>5.1</v>
+        <v>10.6</v>
       </c>
       <c r="G66" s="24" t="n">
-        <v>8.1</v>
+        <v>11.9</v>
       </c>
       <c r="H66" s="24" t="n">
-        <v>87.5</v>
+        <v>10.8</v>
       </c>
       <c r="I66" s="24" t="n">
-        <v>143.9</v>
+        <v>16.7</v>
       </c>
       <c r="J66" s="24" t="n">
-        <v>48.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K66" s="24" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="L66" s="24" t="n">
-        <v>17.1</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -28249,32 +28160,29 @@
       <c r="C67" s="5" t="inlineStr"/>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>令和27年度</t>
-        </is>
-      </c>
-      <c r="E67" s="25" t="n">
-        <v>342.5</v>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="E67" s="24" t="n">
+        <v>3.6</v>
       </c>
       <c r="F67" s="24" t="n">
-        <v>5</v>
+        <v>10.6</v>
       </c>
       <c r="G67" s="24" t="n">
-        <v>7.8</v>
+        <v>11.9</v>
       </c>
       <c r="H67" s="24" t="n">
-        <v>83.8</v>
+        <v>10.8</v>
       </c>
       <c r="I67" s="24" t="n">
-        <v>137.4</v>
+        <v>16.7</v>
       </c>
       <c r="J67" s="24" t="n">
-        <v>45.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K67" s="24" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="L67" s="24" t="n">
-        <v>16.4</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -28283,77 +28191,60 @@
       <c r="C68" s="5" t="inlineStr"/>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>令和32年度</t>
-        </is>
-      </c>
-      <c r="E68" s="25" t="n">
-        <v>340.6</v>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="E68" s="24" t="n">
+        <v>3.6</v>
       </c>
       <c r="F68" s="24" t="n">
-        <v>5</v>
+        <v>10.6</v>
       </c>
       <c r="G68" s="24" t="n">
-        <v>7.9</v>
+        <v>11.9</v>
       </c>
       <c r="H68" s="24" t="n">
-        <v>83.2</v>
+        <v>10.8</v>
       </c>
       <c r="I68" s="24" t="n">
-        <v>136.7</v>
+        <v>16.7</v>
       </c>
       <c r="J68" s="24" t="n">
-        <v>45.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K68" s="24" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="L68" s="24" t="n">
-        <v>16.2</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>短期入所療養介護（老健）</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>令和7年度
-（実績）</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="F69" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G69" s="25" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H69" s="25" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="I69" s="25" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J69" s="25" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="K69" s="25" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="L69" s="25" t="n">
-        <v>7.2</v>
+      <c r="A69" s="5" t="inlineStr"/>
+      <c r="B69" s="5" t="inlineStr"/>
+      <c r="C69" s="5" t="inlineStr"/>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="E69" s="24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F69" s="24" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="G69" s="24" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H69" s="24" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I69" s="24" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J69" s="24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K69" s="24" t="n">
+        <v>11.3</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -28362,66 +28253,71 @@
       <c r="C70" s="5" t="inlineStr"/>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="E70" s="25" t="n">
-        <v>102.7</v>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="E70" s="24" t="n">
+        <v>3.6</v>
       </c>
       <c r="F70" s="24" t="n">
-        <v>1.5</v>
+        <v>10.6</v>
       </c>
       <c r="G70" s="24" t="n">
-        <v>0.3</v>
+        <v>11.9</v>
       </c>
       <c r="H70" s="24" t="n">
-        <v>17.7</v>
+        <v>10.8</v>
       </c>
       <c r="I70" s="24" t="n">
-        <v>32.4</v>
+        <v>16.7</v>
       </c>
       <c r="J70" s="24" t="n">
-        <v>17.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K70" s="24" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="L70" s="24" t="n">
-        <v>7.3</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="5" t="inlineStr"/>
-      <c r="B71" s="5" t="inlineStr"/>
-      <c r="C71" s="5" t="inlineStr"/>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
+      <c r="A71" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>短期入所療養介護（老健）</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>令和7年度
+（実績）</t>
         </is>
       </c>
       <c r="E71" s="25" t="n">
-        <v>103.9</v>
-      </c>
-      <c r="F71" s="24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G71" s="24" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H71" s="24" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="I71" s="24" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="J71" s="24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="K71" s="24" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="L71" s="24" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
+      </c>
+      <c r="F71" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H71" s="25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I71" s="25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J71" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K71" s="25" t="n">
+        <v>5.1</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -28430,32 +28326,29 @@
       <c r="C72" s="5" t="inlineStr"/>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="E72" s="25" t="n">
-        <v>105</v>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E72" s="24" t="n">
+        <v>3.8</v>
       </c>
       <c r="F72" s="24" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G72" s="24" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="H72" s="24" t="n">
-        <v>18.1</v>
+        <v>5.1</v>
       </c>
       <c r="I72" s="24" t="n">
-        <v>33.1</v>
+        <v>7.2</v>
       </c>
       <c r="J72" s="24" t="n">
-        <v>17.7</v>
+        <v>8.5</v>
       </c>
       <c r="K72" s="24" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="L72" s="24" t="n">
-        <v>7.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -28464,32 +28357,29 @@
       <c r="C73" s="5" t="inlineStr"/>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>令和12年度</t>
-        </is>
-      </c>
-      <c r="E73" s="25" t="n">
-        <v>105.8</v>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E73" s="24" t="n">
+        <v>3.8</v>
       </c>
       <c r="F73" s="24" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G73" s="24" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="H73" s="24" t="n">
-        <v>18.2</v>
+        <v>5.1</v>
       </c>
       <c r="I73" s="24" t="n">
-        <v>33.4</v>
+        <v>7.2</v>
       </c>
       <c r="J73" s="24" t="n">
-        <v>17.9</v>
+        <v>8.5</v>
       </c>
       <c r="K73" s="24" t="n">
-        <v>27</v>
-      </c>
-      <c r="L73" s="24" t="n">
-        <v>7.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -28498,32 +28388,29 @@
       <c r="C74" s="5" t="inlineStr"/>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>令和17年度</t>
-        </is>
-      </c>
-      <c r="E74" s="25" t="n">
-        <v>114.5</v>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E74" s="24" t="n">
+        <v>3.8</v>
       </c>
       <c r="F74" s="24" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="G74" s="24" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="H74" s="24" t="n">
-        <v>19.6</v>
+        <v>5.1</v>
       </c>
       <c r="I74" s="24" t="n">
-        <v>36.1</v>
+        <v>7.2</v>
       </c>
       <c r="J74" s="24" t="n">
-        <v>19.5</v>
+        <v>8.5</v>
       </c>
       <c r="K74" s="24" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="L74" s="24" t="n">
-        <v>8.1</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -28532,32 +28419,29 @@
       <c r="C75" s="5" t="inlineStr"/>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>令和22年度</t>
-        </is>
-      </c>
-      <c r="E75" s="25" t="n">
-        <v>118</v>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="E75" s="24" t="n">
+        <v>3.8</v>
       </c>
       <c r="F75" s="24" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="G75" s="24" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="H75" s="24" t="n">
-        <v>20.2</v>
+        <v>5.1</v>
       </c>
       <c r="I75" s="24" t="n">
-        <v>37.2</v>
+        <v>7.2</v>
       </c>
       <c r="J75" s="24" t="n">
-        <v>20.2</v>
+        <v>8.5</v>
       </c>
       <c r="K75" s="24" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="L75" s="24" t="n">
-        <v>8.300000000000001</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -28566,32 +28450,29 @@
       <c r="C76" s="5" t="inlineStr"/>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>令和27年度</t>
-        </is>
-      </c>
-      <c r="E76" s="25" t="n">
-        <v>112.7</v>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="E76" s="24" t="n">
+        <v>3.8</v>
       </c>
       <c r="F76" s="24" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="G76" s="24" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="H76" s="24" t="n">
-        <v>19.3</v>
+        <v>5.1</v>
       </c>
       <c r="I76" s="24" t="n">
-        <v>35.5</v>
+        <v>7.2</v>
       </c>
       <c r="J76" s="24" t="n">
-        <v>19.2</v>
+        <v>8.5</v>
       </c>
       <c r="K76" s="24" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="L76" s="24" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -28600,77 +28481,60 @@
       <c r="C77" s="5" t="inlineStr"/>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>令和32年度</t>
-        </is>
-      </c>
-      <c r="E77" s="25" t="n">
-        <v>112</v>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="n">
+        <v>3.8</v>
       </c>
       <c r="F77" s="24" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="G77" s="24" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="H77" s="24" t="n">
-        <v>19.1</v>
+        <v>5.1</v>
       </c>
       <c r="I77" s="24" t="n">
-        <v>35.4</v>
+        <v>7.2</v>
       </c>
       <c r="J77" s="24" t="n">
-        <v>19</v>
+        <v>8.5</v>
       </c>
       <c r="K77" s="24" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="L77" s="24" t="n">
-        <v>7.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>短期入所療養介護（病院等）</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="D78" s="11" t="inlineStr">
-        <is>
-          <t>令和7年度
-（実績）</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="25" t="n">
-        <v>0</v>
+      <c r="A78" s="5" t="inlineStr"/>
+      <c r="B78" s="5" t="inlineStr"/>
+      <c r="C78" s="5" t="inlineStr"/>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="E78" s="24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F78" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" s="24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I78" s="24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J78" s="24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K78" s="24" t="n">
+        <v>5.1</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -28679,66 +28543,85 @@
       <c r="C79" s="5" t="inlineStr"/>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="E79" s="25" t="n">
-        <v>0</v>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="n">
+        <v>3.8</v>
       </c>
       <c r="F79" s="24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G79" s="24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H79" s="24" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I79" s="24" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J79" s="24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="K79" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="24" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="5" t="inlineStr"/>
-      <c r="B80" s="5" t="inlineStr"/>
-      <c r="C80" s="5" t="inlineStr"/>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="E80" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="24" t="n">
-        <v>0</v>
+      <c r="A80" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>短期入所療養介護（病院等）</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>令和7年度
+（実績）</t>
+        </is>
+      </c>
+      <c r="E80" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F80" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G80" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H80" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I80" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J80" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K80" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -28747,32 +28630,43 @@
       <c r="C81" s="5" t="inlineStr"/>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="E81" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="24" t="n">
-        <v>0</v>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F81" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H81" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I81" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J81" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K81" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -28781,32 +28675,43 @@
       <c r="C82" s="5" t="inlineStr"/>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>令和12年度</t>
-        </is>
-      </c>
-      <c r="E82" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="24" t="n">
-        <v>0</v>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E82" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F82" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G82" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H82" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I82" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J82" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K82" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -28815,32 +28720,43 @@
       <c r="C83" s="5" t="inlineStr"/>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>令和17年度</t>
-        </is>
-      </c>
-      <c r="E83" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="24" t="n">
-        <v>0</v>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F83" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H83" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I83" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J83" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K83" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -28849,32 +28765,43 @@
       <c r="C84" s="5" t="inlineStr"/>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>令和22年度</t>
-        </is>
-      </c>
-      <c r="E84" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="24" t="n">
-        <v>0</v>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="E84" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F84" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G84" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H84" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I84" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J84" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K84" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -28883,32 +28810,43 @@
       <c r="C85" s="5" t="inlineStr"/>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>令和27年度</t>
-        </is>
-      </c>
-      <c r="E85" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="24" t="n">
-        <v>0</v>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F85" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H85" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I85" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J85" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K85" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -28917,77 +28855,88 @@
       <c r="C86" s="5" t="inlineStr"/>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>令和32年度</t>
-        </is>
-      </c>
-      <c r="E86" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="24" t="n">
-        <v>0</v>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="E86" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F86" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G86" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H86" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I86" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J86" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K86" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>短期入所療養介護（介護医療院）</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="D87" s="11" t="inlineStr">
-        <is>
-          <t>令和7年度
-（実績）</t>
-        </is>
-      </c>
-      <c r="E87" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="25" t="n">
-        <v>0</v>
+      <c r="A87" s="5" t="inlineStr"/>
+      <c r="B87" s="5" t="inlineStr"/>
+      <c r="C87" s="5" t="inlineStr"/>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="E87" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F87" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G87" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H87" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I87" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J87" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K87" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -28996,66 +28945,99 @@
       <c r="C88" s="5" t="inlineStr"/>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="E88" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="24" t="n">
-        <v>0</v>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="E88" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F88" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G88" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H88" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I88" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J88" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K88" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="5" t="inlineStr"/>
-      <c r="B89" s="5" t="inlineStr"/>
-      <c r="C89" s="5" t="inlineStr"/>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="E89" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="24" t="n">
-        <v>0</v>
+      <c r="A89" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>短期入所療養介護（介護医療院）</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>令和7年度
+（実績）</t>
+        </is>
+      </c>
+      <c r="E89" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F89" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G89" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H89" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I89" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J89" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K89" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -29064,32 +29046,43 @@
       <c r="C90" s="5" t="inlineStr"/>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="E90" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="24" t="n">
-        <v>0</v>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E90" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F90" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G90" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H90" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I90" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J90" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K90" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -29098,32 +29091,43 @@
       <c r="C91" s="5" t="inlineStr"/>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>令和12年度</t>
-        </is>
-      </c>
-      <c r="E91" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="24" t="n">
-        <v>0</v>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F91" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H91" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I91" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J91" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K91" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -29132,32 +29136,43 @@
       <c r="C92" s="5" t="inlineStr"/>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>令和17年度</t>
-        </is>
-      </c>
-      <c r="E92" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="24" t="n">
-        <v>0</v>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E92" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F92" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G92" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H92" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I92" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J92" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K92" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -29166,32 +29181,43 @@
       <c r="C93" s="5" t="inlineStr"/>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>令和22年度</t>
-        </is>
-      </c>
-      <c r="E93" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="24" t="n">
-        <v>0</v>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="E93" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F93" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G93" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H93" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I93" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J93" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K93" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -29200,32 +29226,43 @@
       <c r="C94" s="5" t="inlineStr"/>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>令和27年度</t>
-        </is>
-      </c>
-      <c r="E94" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="24" t="n">
-        <v>0</v>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="E94" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F94" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G94" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H94" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I94" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J94" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K94" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -29234,222 +29271,239 @@
       <c r="C95" s="5" t="inlineStr"/>
       <c r="D95" s="5" t="inlineStr">
         <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="E95" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F95" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G95" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H95" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I95" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J95" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K95" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="5" t="inlineStr"/>
+      <c r="B96" s="5" t="inlineStr"/>
+      <c r="C96" s="5" t="inlineStr"/>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="E96" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F96" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G96" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H96" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I96" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J96" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K96" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="5" t="inlineStr"/>
+      <c r="B97" s="5" t="inlineStr"/>
+      <c r="C97" s="5" t="inlineStr"/>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
           <t>令和32年度</t>
         </is>
       </c>
-      <c r="E95" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>（２）地域密着型サービス　利用回（日）数（回・日／月・小数第1位）</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="4" t="inlineStr"/>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>サービス</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="E97" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F97" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G97" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H97" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I97" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J97" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K97" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>（２）地域密着型サービス　【入力】1人1月あたりの利用回（日）数（回・日／月・小数第1位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="4" t="inlineStr"/>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>サービス（プルダウンで選ぶ）</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="D99" s="4" t="inlineStr">
         <is>
           <t>年度</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="E99" s="4" t="inlineStr">
         <is>
           <t>要支援1</t>
         </is>
       </c>
-      <c r="G97" s="4" t="inlineStr">
+      <c r="F99" s="4" t="inlineStr">
         <is>
           <t>要支援2</t>
         </is>
       </c>
-      <c r="H97" s="4" t="inlineStr">
+      <c r="G99" s="4" t="inlineStr">
         <is>
           <t>要介護1</t>
         </is>
       </c>
-      <c r="I97" s="4" t="inlineStr">
+      <c r="H99" s="4" t="inlineStr">
         <is>
           <t>要介護2</t>
         </is>
       </c>
-      <c r="J97" s="4" t="inlineStr">
+      <c r="I99" s="4" t="inlineStr">
         <is>
           <t>要介護3</t>
         </is>
       </c>
-      <c r="K97" s="4" t="inlineStr">
+      <c r="J99" s="4" t="inlineStr">
         <is>
           <t>要介護4</t>
         </is>
       </c>
-      <c r="L97" s="4" t="inlineStr">
+      <c r="K99" s="4" t="inlineStr">
         <is>
           <t>要介護5</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="5" t="n">
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>地域密着型通所介護</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>回</t>
         </is>
       </c>
-      <c r="D98" s="11" t="inlineStr">
+      <c r="D100" s="11" t="inlineStr">
         <is>
           <t>令和7年度
 （実績）</t>
         </is>
       </c>
-      <c r="E98" s="30" t="n">
-        <v>600.7</v>
-      </c>
-      <c r="F98" s="25" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G98" s="25" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="H98" s="25" t="n">
-        <v>292.4</v>
-      </c>
-      <c r="I98" s="25" t="n">
-        <v>186</v>
-      </c>
-      <c r="J98" s="25" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="K98" s="25" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="L98" s="25" t="n">
-        <v>23.7</v>
-      </c>
-    </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="5" t="inlineStr"/>
-      <c r="B99" s="5" t="inlineStr"/>
-      <c r="C99" s="5" t="inlineStr"/>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="E99" s="25" t="n">
-        <v>613.3</v>
-      </c>
-      <c r="F99" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G99" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="H99" s="24" t="n">
-        <v>298.2</v>
-      </c>
-      <c r="I99" s="24" t="n">
-        <v>190.1</v>
-      </c>
-      <c r="J99" s="24" t="n">
-        <v>70</v>
-      </c>
-      <c r="K99" s="24" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="L99" s="24" t="n">
-        <v>24.1</v>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="5" t="inlineStr"/>
-      <c r="B100" s="5" t="inlineStr"/>
-      <c r="C100" s="5" t="inlineStr"/>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="E100" s="25" t="n">
-        <v>619.8</v>
-      </c>
-      <c r="F100" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G100" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="H100" s="24" t="n">
-        <v>301.1</v>
-      </c>
-      <c r="I100" s="24" t="n">
-        <v>192.2</v>
-      </c>
-      <c r="J100" s="24" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="K100" s="24" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="L100" s="24" t="n">
-        <v>24.4</v>
+      <c r="E100" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F100" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G100" s="25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H100" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I100" s="25" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J100" s="25" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="K100" s="25" t="n">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -29458,36 +29512,33 @@
       <c r="C101" s="5" t="inlineStr"/>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="E101" s="25" t="n">
-        <v>626.4</v>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E101" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F101" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G101" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G101" s="24" t="n">
+        <v>6.8</v>
       </c>
       <c r="H101" s="24" t="n">
-        <v>304.1</v>
+        <v>8.5</v>
       </c>
       <c r="I101" s="24" t="n">
-        <v>194.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J101" s="24" t="n">
-        <v>71.7</v>
+        <v>10.7</v>
       </c>
       <c r="K101" s="24" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="L101" s="24" t="n">
-        <v>24.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -29496,36 +29547,33 @@
       <c r="C102" s="5" t="inlineStr"/>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>令和12年度</t>
-        </is>
-      </c>
-      <c r="E102" s="25" t="n">
-        <v>631.1</v>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E102" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F102" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G102" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G102" s="24" t="n">
+        <v>6.8</v>
       </c>
       <c r="H102" s="24" t="n">
-        <v>306.2</v>
+        <v>8.5</v>
       </c>
       <c r="I102" s="24" t="n">
-        <v>195.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J102" s="24" t="n">
-        <v>72.3</v>
+        <v>10.7</v>
       </c>
       <c r="K102" s="24" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="L102" s="24" t="n">
-        <v>24.8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -29534,36 +29582,33 @@
       <c r="C103" s="5" t="inlineStr"/>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>令和17年度</t>
-        </is>
-      </c>
-      <c r="E103" s="25" t="n">
-        <v>681.1</v>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E103" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F103" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G103" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G103" s="24" t="n">
+        <v>6.8</v>
       </c>
       <c r="H103" s="24" t="n">
-        <v>328.8</v>
+        <v>8.5</v>
       </c>
       <c r="I103" s="24" t="n">
-        <v>211.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J103" s="24" t="n">
-        <v>79.09999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="K103" s="24" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="L103" s="24" t="n">
-        <v>26.7</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -29572,36 +29617,33 @@
       <c r="C104" s="5" t="inlineStr"/>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>令和22年度</t>
-        </is>
-      </c>
-      <c r="E104" s="25" t="n">
-        <v>701.7</v>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="E104" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F104" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G104" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G104" s="24" t="n">
+        <v>6.8</v>
       </c>
       <c r="H104" s="24" t="n">
-        <v>338.6</v>
+        <v>8.5</v>
       </c>
       <c r="I104" s="24" t="n">
-        <v>218.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J104" s="24" t="n">
-        <v>81.7</v>
+        <v>10.7</v>
       </c>
       <c r="K104" s="24" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="L104" s="24" t="n">
-        <v>27.5</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -29610,36 +29652,33 @@
       <c r="C105" s="5" t="inlineStr"/>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>令和27年度</t>
-        </is>
-      </c>
-      <c r="E105" s="25" t="n">
-        <v>671</v>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="E105" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F105" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G105" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G105" s="24" t="n">
+        <v>6.8</v>
       </c>
       <c r="H105" s="24" t="n">
-        <v>324.6</v>
+        <v>8.5</v>
       </c>
       <c r="I105" s="24" t="n">
-        <v>208.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J105" s="24" t="n">
-        <v>77.59999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="K105" s="24" t="n">
-        <v>34</v>
-      </c>
-      <c r="L105" s="24" t="n">
-        <v>26.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -29648,81 +29687,68 @@
       <c r="C106" s="5" t="inlineStr"/>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>令和32年度</t>
-        </is>
-      </c>
-      <c r="E106" s="25" t="n">
-        <v>666.4</v>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="E106" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="F106" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G106" s="24" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="G106" s="24" t="n">
+        <v>6.8</v>
       </c>
       <c r="H106" s="24" t="n">
-        <v>322</v>
+        <v>8.5</v>
       </c>
       <c r="I106" s="24" t="n">
-        <v>207.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J106" s="24" t="n">
-        <v>77.09999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="K106" s="24" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="L106" s="24" t="n">
-        <v>26.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>認知症対応型通所介護</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>回</t>
-        </is>
-      </c>
-      <c r="D107" s="11" t="inlineStr">
-        <is>
-          <t>令和7年度
-（実績）</t>
-        </is>
-      </c>
-      <c r="E107" s="30" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="F107" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="25" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J107" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="25" t="n">
-        <v>0</v>
+      <c r="A107" s="5" t="inlineStr"/>
+      <c r="B107" s="5" t="inlineStr"/>
+      <c r="C107" s="5" t="inlineStr"/>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="E107" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F107" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G107" s="24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H107" s="24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I107" s="24" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J107" s="24" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="K107" s="24" t="n">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -29731,66 +29757,87 @@
       <c r="C108" s="5" t="inlineStr"/>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="E108" s="25" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="F108" s="24" t="n">
-        <v>0</v>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="E108" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F108" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G108" s="24" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="H108" s="24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="I108" s="24" t="n">
-        <v>8.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J108" s="24" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="K108" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="24" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="5" t="inlineStr"/>
-      <c r="B109" s="5" t="inlineStr"/>
-      <c r="C109" s="5" t="inlineStr"/>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="E109" s="25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="F109" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" s="24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J109" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="24" t="n">
-        <v>0</v>
+      <c r="A109" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>令和7年度
+（実績）</t>
+        </is>
+      </c>
+      <c r="E109" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F109" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G109" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H109" s="25" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I109" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J109" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K109" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -29799,32 +29846,41 @@
       <c r="C110" s="5" t="inlineStr"/>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="E110" s="25" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="F110" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" s="24" t="n">
-        <v>0</v>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E110" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F110" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G110" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="H110" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="24" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J110" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="24" t="n">
-        <v>0</v>
+        <v>7.9</v>
+      </c>
+      <c r="I110" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J110" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K110" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -29833,32 +29889,41 @@
       <c r="C111" s="5" t="inlineStr"/>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>令和12年度</t>
-        </is>
-      </c>
-      <c r="E111" s="25" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="F111" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" s="24" t="n">
-        <v>0</v>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E111" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F111" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G111" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="H111" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="24" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J111" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="24" t="n">
-        <v>0</v>
+        <v>7.9</v>
+      </c>
+      <c r="I111" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J111" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K111" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -29867,32 +29932,41 @@
       <c r="C112" s="5" t="inlineStr"/>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>令和17年度</t>
-        </is>
-      </c>
-      <c r="E112" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="F112" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" s="24" t="n">
-        <v>0</v>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E112" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F112" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G112" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="H112" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" s="24" t="n">
-        <v>9</v>
-      </c>
-      <c r="J112" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="24" t="n">
-        <v>0</v>
+        <v>7.9</v>
+      </c>
+      <c r="I112" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J112" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K112" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -29901,32 +29975,41 @@
       <c r="C113" s="5" t="inlineStr"/>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>令和22年度</t>
-        </is>
-      </c>
-      <c r="E113" s="25" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="F113" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="24" t="n">
-        <v>0</v>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="E113" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F113" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G113" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="H113" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" s="24" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J113" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="24" t="n">
-        <v>0</v>
+        <v>7.9</v>
+      </c>
+      <c r="I113" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J113" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K113" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -29935,32 +30018,41 @@
       <c r="C114" s="5" t="inlineStr"/>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>令和27年度</t>
-        </is>
-      </c>
-      <c r="E114" s="25" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="F114" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" s="24" t="n">
-        <v>0</v>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="E114" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F114" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G114" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="H114" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" s="24" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J114" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="24" t="n">
-        <v>0</v>
+        <v>7.9</v>
+      </c>
+      <c r="I114" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J114" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K114" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -29969,50 +30061,148 @@
       <c r="C115" s="5" t="inlineStr"/>
       <c r="D115" s="5" t="inlineStr">
         <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="E115" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F115" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G115" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H115" s="24" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I115" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J115" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K115" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="5" t="inlineStr"/>
+      <c r="B116" s="5" t="inlineStr"/>
+      <c r="C116" s="5" t="inlineStr"/>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="E116" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F116" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G116" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H116" s="24" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I116" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J116" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K116" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="5" t="inlineStr"/>
+      <c r="B117" s="5" t="inlineStr"/>
+      <c r="C117" s="5" t="inlineStr"/>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
           <t>令和32年度</t>
         </is>
       </c>
-      <c r="E115" s="25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="F115" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" s="24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J115" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" ht="52" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
+      <c r="E117" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F117" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G117" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H117" s="24" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I117" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J117" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K117" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="90" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>注1）本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。
-注2）通所介護・地域密着型通所介護・通所リハビリテーション・認知症対応型通所介護の単位は「回」です（年報・総括表による）。短期入所2種別は「日」です。
-注3）月包括報酬によるもの・支給決定によるものは回（日）数の計上がないため掲げていません。</t>
+注2）1人1月あたりを令和7年度で固定しているため、令和9年度以降は令和7年度と同じ値になります。利用者数の側が動くことにより延べの回（日）数は年度ごとに変わります。
+注3）年報（令和7年度）の要介護度別の利用回（日）数を同じ区分の受給者数で除して求めた値です。画面が令和7年度に表示している値と一致します（14シート 点検23）。
+注4）通所介護・地域密着型通所介護・通所リハビリテーション・認知症対応型通所介護の単位は「回」です（年報・総括表による）。短期入所2種別は「日」です。
+注5）「―」は画面にその要介護度の列がないものです。画面と同じく合計の列は置いていません（1人1月あたりは各列の和になりません）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A96:L96"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A116:L116"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A4:L4"/>
+  <mergeCells count="6">
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A118:K118"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A98:K98"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/output/第10期計画_見える化_入力箇所と入力値.xlsx
+++ b/output/第10期計画_見える化_入力箇所と入力値.xlsx
@@ -4369,7 +4369,7 @@
       </c>
       <c r="C16" s="42" t="inlineStr">
         <is>
-          <t>9,031,900,443.929735円</t>
+          <t>9,035,114,142.285852円</t>
         </is>
       </c>
       <c r="D16" s="27" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="C17" s="42" t="inlineStr">
         <is>
-          <t>9,565,616,320.672682円</t>
+          <t>9,569,019,923.893934円</t>
         </is>
       </c>
       <c r="D17" s="27" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="C18" s="42" t="inlineStr">
         <is>
-          <t>6,436.09円</t>
+          <t>6,438.26円</t>
         </is>
       </c>
       <c r="D18" s="27" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="C20" s="42" t="inlineStr">
         <is>
-          <t>計画本文は20,927.6回・日／月</t>
+          <t>計画本文は20,942.4回・日／月</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>画面は1人1月あたりを要介護度別に入れるため、システムが求める延べは要介護度の構成の動きを取り込みます。計画本文は要支援・要介護の群でまとめた1人1月あたりによっており、差は最大 +0.09％（訪問介護）です。保険料には入りません</t>
+          <t>画面は1人1月あたりを要介護度別に入れるため、システムが求める延べは要介護度の構成の動きを取り込みます。計画本文は要支援・要介護の群でまとめた1人1月あたりによっており、差は最大 +0.00％（―）です。保険料には入りません</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_見える化_入力箇所と入力値.xlsx
+++ b/output/第10期計画_見える化_入力箇所と入力値.xlsx
@@ -1771,7 +1771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3019,11 +3019,159 @@
       <c r="H62" s="8" t="inlineStr"/>
       <c r="I62" s="8" t="inlineStr"/>
     </row>
-    <row r="63" ht="92" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
+    <row r="63"/>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>参考2　令和12年度以降（別画面。自然体推計値の確認と施策反映値の入力）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="4" t="inlineStr"/>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>事業区分</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>介護予防・日常生活支援総合事業費</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>事業費（円）</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="n">
+        <v>112479138</v>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v>120299137</v>
+      </c>
+      <c r="F66" s="14" t="n">
+        <v>123552614</v>
+      </c>
+      <c r="G66" s="14" t="n">
+        <v>118576472</v>
+      </c>
+      <c r="H66" s="14" t="n">
+        <v>118244825</v>
+      </c>
+      <c r="I66" s="5" t="inlineStr"/>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>包括的支援事業（地域包括支援センターの運営）及び任意事業費並びに包括的支援事業（社会保障充実分）</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>事業費（円）</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="n">
+        <v>70967498</v>
+      </c>
+      <c r="E67" s="14" t="n">
+        <v>71263644</v>
+      </c>
+      <c r="F67" s="14" t="n">
+        <v>73123779</v>
+      </c>
+      <c r="G67" s="14" t="n">
+        <v>72382081</v>
+      </c>
+      <c r="H67" s="14" t="n">
+        <v>70317509</v>
+      </c>
+      <c r="I67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>地域支援事業費（計）</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>事業費（円）</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="n">
+        <v>183446636</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>191562781</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>196676393</v>
+      </c>
+      <c r="G68" s="10" t="n">
+        <v>190958553</v>
+      </c>
+      <c r="H68" s="10" t="n">
+        <v>188562334</v>
+      </c>
+      <c r="I68" s="8" t="inlineStr"/>
+    </row>
+    <row r="69" ht="64" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>中長期は量の見込みと同じ伸びで延ばしています（介護予防・日常生活支援総合事業費は認定者数、そのほかは第1号被保険者数）。
+群ごとに分けて入れてください。調整交付金相当額及び調整交付金見込額の算定基礎には「介護予防・日常生活支援総合事業費」のみが入るため、計をまとめて1つの事業に置くと調整交付金の額が変わります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="92" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>注1）本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。
-注2）令和6年度決算の水準を3年据え置いたものです。この額を入れると算定上の月額が約＋332円上がります。
+注2）令和6年度決算の水準を3年据え置いたものです。この額を入れると算定上の月額が約＋353円上がります（当方の算定の基礎による。見える化の補正後被保険者数で計算するとこれと異なります）。
 注3）保険者機能強化推進事業費及び保険者努力支援事業費はこの額から除いています（令和6年度決算の款4の全体183,384,259円から2事業を除いた額が177,161,259円）。このため、手順8の「保険者機能強化推進交付金等の交付見込額」の欄は0のままとします。両方を行うと二重控除になります（確認事項No.86）。
 注4）特定地域居宅サービス等事業・介護情報利活用事業は令和9年4月の新設であり、令和6年度から令和8年度は「―」です。額が定まらないため空欄とします。
 注5）令和12年度以降は「地域支援事業費の自然体推計値の確認と施策反映値の入力」という別の画面です。</t>
@@ -3031,16 +3179,18 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
+    <mergeCell ref="A64:I64"/>
     <mergeCell ref="A43:I43"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A63:I63"/>
     <mergeCell ref="A46:I46"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A70:I70"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="A58:I58"/>
+    <mergeCell ref="A69:I69"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A4:I4"/>
   </mergeCells>
@@ -3063,7 +3213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3907,7 +4057,7 @@
 注2）割合は公費軽減前の値です。第1段階から第3段階は公費軽減の対象ですが、補正後被保険者数はこの割合で算定します。公費軽減後の値（第1段階0.285など）は入れません。
 注3）基準所得金額は第7段階から第16段階の10件です。第1段階から第6段階は本人の合計所得金額の下限による区分ではないため、画面も当該欄を受け付けません。
 注4）計は「実績及び推計方法の設定」の第1号被保険者数と一致させます（02シートの値）。一致していないと登録できません。
-注5）第17段階から第30段階は空欄のままとします。
+注5）第17段階から第40段階は空欄のままとします。弾力化の段階は令和8年9月30日に30段階から40段階へ拡張されました。
 注6）第10期の段階数・割合・基準所得金額は政令改正により変わり得ます（確認事項No.33）。保険料段階の基準額を80.9万円から82.65万円に改める政令改正が済んでおり、条例改正の手続を要します。</t>
         </is>
       </c>
@@ -3916,158 +4066,983 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>1-2　人口の設定を改めない場合の所得段階別第1号被保険者数</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="76" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>直近の推計（推計名1006）は人口の設定が社人研推計のままであり、画面が表示する第1号被保険者数は1の表の計と31人から134人の幅で異なります。人口の設定を案Cに改めないまま1の表の人数を入れると、計が一致せず登録できません。人口の設定を先に改めることをお勧めしますが、改めない場合は本表の人数を入れてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>段階</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>対象者要件</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>割合</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>基準所得金額（円）</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>第1段階</t>
+        </is>
+      </c>
+      <c r="C29" s="36" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>1457</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>1456</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>1456</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>1456</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>1465</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>1499</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>1482</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>第2段階</t>
+        </is>
+      </c>
+      <c r="C30" s="36" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>1174</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>1173</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>1172</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>1172</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>1180</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>1207</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>1193</v>
+      </c>
+      <c r="L30" s="14" t="n">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>第3段階</t>
+        </is>
+      </c>
+      <c r="C31" s="36" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>934</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>933</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>933</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>933</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>939</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>960</v>
+      </c>
+      <c r="K31" s="14" t="n">
+        <v>950</v>
+      </c>
+      <c r="L31" s="14" t="n">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>第4段階</t>
+        </is>
+      </c>
+      <c r="C32" s="36" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>750</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>750</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>750</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>750</v>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>755</v>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>772</v>
+      </c>
+      <c r="K32" s="14" t="n">
+        <v>763</v>
+      </c>
+      <c r="L32" s="14" t="n">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>第5段階（基準）</t>
+        </is>
+      </c>
+      <c r="C33" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>1180</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>1180</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>1179</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>1179</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>1187</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>1214</v>
+      </c>
+      <c r="K33" s="14" t="n">
+        <v>1201</v>
+      </c>
+      <c r="L33" s="14" t="n">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>第6段階</t>
+        </is>
+      </c>
+      <c r="C34" s="36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>1377</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>1376</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>1376</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>1385</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>1417</v>
+      </c>
+      <c r="K34" s="14" t="n">
+        <v>1401</v>
+      </c>
+      <c r="L34" s="14" t="n">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>第7段階</t>
+        </is>
+      </c>
+      <c r="C35" s="36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>1229</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>1228</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <v>1228</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>1228</v>
+      </c>
+      <c r="I35" s="14" t="n">
+        <v>1236</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>1264</v>
+      </c>
+      <c r="K35" s="14" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L35" s="14" t="n">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>第8段階</t>
+        </is>
+      </c>
+      <c r="C36" s="36" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>526</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>525</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>525</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>525</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <v>529</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>541</v>
+      </c>
+      <c r="K36" s="14" t="n">
+        <v>534</v>
+      </c>
+      <c r="L36" s="14" t="n">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>第9段階</t>
+        </is>
+      </c>
+      <c r="C37" s="36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>202</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>202</v>
+      </c>
+      <c r="G37" s="14" t="n">
+        <v>202</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>202</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>203</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>208</v>
+      </c>
+      <c r="K37" s="14" t="n">
+        <v>206</v>
+      </c>
+      <c r="L37" s="14" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>第10段階</t>
+        </is>
+      </c>
+      <c r="C38" s="36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="G38" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="J38" s="14" t="n">
+        <v>102</v>
+      </c>
+      <c r="K38" s="14" t="n">
+        <v>101</v>
+      </c>
+      <c r="L38" s="14" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>第11段階</t>
+        </is>
+      </c>
+      <c r="C39" s="36" t="n">
+        <v>2.165</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="G39" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="J39" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="K39" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L39" s="14" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>第12段階</t>
+        </is>
+      </c>
+      <c r="C40" s="36" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G40" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="I40" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="J40" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K40" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="L40" s="14" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>第13段階</t>
+        </is>
+      </c>
+      <c r="C41" s="36" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G41" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="J41" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K41" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="L41" s="14" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>第14段階</t>
+        </is>
+      </c>
+      <c r="C42" s="36" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>8200000</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I42" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="J42" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="K42" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="L42" s="14" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>第15段階</t>
+        </is>
+      </c>
+      <c r="C43" s="36" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="G43" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I43" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="J43" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="K43" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="L43" s="14" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>第16段階</t>
+        </is>
+      </c>
+      <c r="C44" s="36" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>10200000</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="G44" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="I44" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="J44" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="K44" s="14" t="n">
+        <v>67</v>
+      </c>
+      <c r="L44" s="14" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="37" t="inlineStr"/>
+      <c r="B45" s="37" t="inlineStr">
+        <is>
+          <t>計（画面が表示する第1号被保険者数）</t>
+        </is>
+      </c>
+      <c r="C45" s="38" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D45" s="38" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E45" s="39" t="n">
+        <v>9116</v>
+      </c>
+      <c r="F45" s="39" t="n">
+        <v>9110</v>
+      </c>
+      <c r="G45" s="39" t="n">
+        <v>9107</v>
+      </c>
+      <c r="H45" s="39" t="n">
+        <v>9106</v>
+      </c>
+      <c r="I45" s="39" t="n">
+        <v>9166</v>
+      </c>
+      <c r="J45" s="39" t="n">
+        <v>9375</v>
+      </c>
+      <c r="K45" s="39" t="n">
+        <v>9270</v>
+      </c>
+      <c r="L45" s="39" t="n">
+        <v>8993</v>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="11" t="inlineStr"/>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>補正後被保険者数（自動計算）</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E46" s="40" t="n">
+        <v>9038.1</v>
+      </c>
+      <c r="F46" s="40" t="n">
+        <v>9032.200000000001</v>
+      </c>
+      <c r="G46" s="40" t="n">
+        <v>9029.299999999999</v>
+      </c>
+      <c r="H46" s="40" t="n">
+        <v>9026.700000000001</v>
+      </c>
+      <c r="I46" s="40" t="n">
+        <v>9086.6</v>
+      </c>
+      <c r="J46" s="40" t="n">
+        <v>9293.200000000001</v>
+      </c>
+      <c r="K46" s="40" t="n">
+        <v>9189.1</v>
+      </c>
+      <c r="L46" s="40" t="n">
+        <v>8915.1</v>
+      </c>
+    </row>
+    <row r="47" ht="64" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>注1）割合及び基準所得金額は1の表と同じです。人数だけが違います。
+注2）構成比は令和6年度の実績によるもので1の表と同じです。総数に構成比を乗じ、合計を保ったまま整数にしています。
+注3）この表で算定すると補正後被保険者数が小さくなるため、保険料基準額は1の表による場合より高く出ます。人口の設定を案Cに改めることをお勧めする理由の一つです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
           <t>2　そのほかの欄</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>入れる値</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="4" t="inlineStr"/>
-      <c r="J27" s="4" t="inlineStr"/>
-      <c r="K27" s="4" t="inlineStr"/>
-      <c r="L27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="5" t="n">
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="inlineStr"/>
+      <c r="J50" s="4" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr"/>
+      <c r="L50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>準備基金取崩額</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>0（当面）</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>令和7年度末の基金残高の提供を受けてから入れます。1億円の取崩しで算定上の月額が約310円下がります</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
-      <c r="L28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="5" t="n">
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr"/>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr"/>
+      <c r="K51" s="5" t="inlineStr"/>
+      <c r="L51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の交付見込額</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>地域支援事業費から2事業を既に除いているため、ここで控除すると二重控除になります（確認事項No.86）</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="5" t="n">
+      <c r="E52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="5" t="inlineStr"/>
+      <c r="K52" s="5" t="inlineStr"/>
+      <c r="L52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>財政安定化基金拠出金見込額・償還金</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>いずれも0です</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="5" t="n">
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="5" t="inlineStr"/>
+      <c r="K53" s="5" t="inlineStr"/>
+      <c r="L53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>市町村特別給付費等</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>当連合では行っていません</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr"/>
+      <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr"/>
+      <c r="K54" s="5" t="inlineStr"/>
+      <c r="L54" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="8">
     <mergeCell ref="A26:L26"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A49:L49"/>
+    <mergeCell ref="A47:L47"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A27:L27"/>
     <mergeCell ref="A4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4519,7 +5494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5220,27 +6195,152 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="8" t="inlineStr"/>
-      <c r="B31" s="8" t="inlineStr">
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>人口の設定を改めない場合の計が画面の第1号被保険者数と一致すること</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>推計1006 の第1号被保険者数</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>9116／9110／9107／9106／9166／9375／9270／8993</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>人口の設定を改めない場合も16段階であること</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>段階数</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>16段階</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>地域支援事業費の群別の和が計と一致すること（中長期）</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>介護予防・日常生活支援総合事業費＋そのほか＝計</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>5年度で一致</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>地域支援事業費の中長期が5年次そろっていること</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>令和12・17・22・27・32年度</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>5年次</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>第10期の地域支援事業費が令和6年度の水準の据え置きであること</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>CHIIKI_R6×3</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>531,483,777円</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="8" t="inlineStr"/>
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>自己点検の結果</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr"/>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>適合26件・不適合0件</t>
-        </is>
-      </c>
-      <c r="E31" s="43" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>適合31件・不適合0件</t>
+        </is>
+      </c>
+      <c r="E36" s="43" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>注）本シートは点検の記録であり、本表の値が暫定値であることを変えるものではありません。</t>
         </is>
@@ -5250,7 +6350,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A37:E37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -6067,7 +7167,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>月額 約＋332円</t>
+          <t>月額 約＋353円</t>
         </is>
       </c>
     </row>
